--- a/output/version3/test/20-15/MARL/CTDE/RL-RL with EP/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-15/MARL/CTDE/RL-RL with EP/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1066</v>
+        <v>1054</v>
       </c>
       <c r="C2" t="n">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="D2" t="n">
-        <v>1087</v>
+        <v>1010</v>
       </c>
       <c r="E2" t="n">
-        <v>883</v>
+        <v>789</v>
       </c>
       <c r="F2" t="n">
-        <v>960</v>
+        <v>818</v>
       </c>
       <c r="G2" t="n">
-        <v>986</v>
+        <v>795</v>
       </c>
       <c r="H2" t="n">
-        <v>941</v>
+        <v>1051</v>
       </c>
       <c r="I2" t="n">
-        <v>942</v>
+        <v>823</v>
       </c>
       <c r="J2" t="n">
-        <v>1086</v>
+        <v>849</v>
       </c>
       <c r="K2" t="n">
-        <v>1202</v>
+        <v>862</v>
       </c>
       <c r="L2" t="n">
-        <v>1003.7</v>
+        <v>894</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>1150</v>
+        <v>861</v>
       </c>
       <c r="C3" t="n">
-        <v>938</v>
+        <v>855</v>
       </c>
       <c r="D3" t="n">
-        <v>1002</v>
+        <v>976</v>
       </c>
       <c r="E3" t="n">
-        <v>1192</v>
+        <v>932</v>
       </c>
       <c r="F3" t="n">
-        <v>1215</v>
+        <v>850</v>
       </c>
       <c r="G3" t="n">
-        <v>1146</v>
+        <v>888</v>
       </c>
       <c r="H3" t="n">
-        <v>1013</v>
+        <v>928</v>
       </c>
       <c r="I3" t="n">
-        <v>1096</v>
+        <v>898</v>
       </c>
       <c r="J3" t="n">
-        <v>1173</v>
+        <v>880</v>
       </c>
       <c r="K3" t="n">
-        <v>1162</v>
+        <v>930</v>
       </c>
       <c r="L3" t="n">
-        <v>1108.7</v>
+        <v>899.8</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>1137</v>
+        <v>1076</v>
       </c>
       <c r="C4" t="n">
-        <v>1122</v>
+        <v>868</v>
       </c>
       <c r="D4" t="n">
-        <v>1069</v>
+        <v>907</v>
       </c>
       <c r="E4" t="n">
-        <v>1029</v>
+        <v>872</v>
       </c>
       <c r="F4" t="n">
-        <v>891</v>
+        <v>735</v>
       </c>
       <c r="G4" t="n">
-        <v>1107</v>
+        <v>845</v>
       </c>
       <c r="H4" t="n">
-        <v>979</v>
+        <v>1071</v>
       </c>
       <c r="I4" t="n">
-        <v>1072</v>
+        <v>960</v>
       </c>
       <c r="J4" t="n">
-        <v>925</v>
+        <v>1042</v>
       </c>
       <c r="K4" t="n">
-        <v>819</v>
+        <v>1026</v>
       </c>
       <c r="L4" t="n">
-        <v>1015</v>
+        <v>940.2</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>1147</v>
+        <v>866</v>
       </c>
       <c r="C5" t="n">
-        <v>972</v>
+        <v>886</v>
       </c>
       <c r="D5" t="n">
-        <v>912</v>
+        <v>867</v>
       </c>
       <c r="E5" t="n">
-        <v>1156</v>
+        <v>810</v>
       </c>
       <c r="F5" t="n">
-        <v>1192</v>
+        <v>830</v>
       </c>
       <c r="G5" t="n">
-        <v>1094</v>
+        <v>876</v>
       </c>
       <c r="H5" t="n">
-        <v>962</v>
+        <v>837</v>
       </c>
       <c r="I5" t="n">
-        <v>959</v>
+        <v>780</v>
       </c>
       <c r="J5" t="n">
-        <v>1088</v>
+        <v>864</v>
       </c>
       <c r="K5" t="n">
-        <v>1083</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>1056.5</v>
+        <v>856.6</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>1123</v>
+        <v>802</v>
       </c>
       <c r="C6" t="n">
-        <v>936</v>
+        <v>773</v>
       </c>
       <c r="D6" t="n">
-        <v>944</v>
+        <v>749</v>
       </c>
       <c r="E6" t="n">
-        <v>1104</v>
+        <v>686</v>
       </c>
       <c r="F6" t="n">
-        <v>1002</v>
+        <v>678</v>
       </c>
       <c r="G6" t="n">
-        <v>900</v>
+        <v>756</v>
       </c>
       <c r="H6" t="n">
-        <v>883</v>
+        <v>865</v>
       </c>
       <c r="I6" t="n">
-        <v>886</v>
+        <v>746</v>
       </c>
       <c r="J6" t="n">
-        <v>960</v>
+        <v>717</v>
       </c>
       <c r="K6" t="n">
-        <v>1129</v>
+        <v>752</v>
       </c>
       <c r="L6" t="n">
-        <v>986.7</v>
+        <v>752.4</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>1103</v>
+        <v>907</v>
       </c>
       <c r="C7" t="n">
-        <v>983</v>
+        <v>1096</v>
       </c>
       <c r="D7" t="n">
-        <v>997</v>
+        <v>1020</v>
       </c>
       <c r="E7" t="n">
-        <v>970</v>
+        <v>818</v>
       </c>
       <c r="F7" t="n">
-        <v>1122</v>
+        <v>786</v>
       </c>
       <c r="G7" t="n">
-        <v>1191</v>
+        <v>853</v>
       </c>
       <c r="H7" t="n">
-        <v>951</v>
+        <v>881</v>
       </c>
       <c r="I7" t="n">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="J7" t="n">
-        <v>1128</v>
+        <v>898</v>
       </c>
       <c r="K7" t="n">
-        <v>1121</v>
+        <v>865</v>
       </c>
       <c r="L7" t="n">
-        <v>1049</v>
+        <v>905.4</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1146</v>
+        <v>720</v>
       </c>
       <c r="C8" t="n">
-        <v>1020</v>
+        <v>743</v>
       </c>
       <c r="D8" t="n">
-        <v>1029</v>
+        <v>1010</v>
       </c>
       <c r="E8" t="n">
-        <v>793</v>
+        <v>813</v>
       </c>
       <c r="F8" t="n">
-        <v>884</v>
+        <v>827</v>
       </c>
       <c r="G8" t="n">
-        <v>1043</v>
+        <v>829</v>
       </c>
       <c r="H8" t="n">
-        <v>1087</v>
+        <v>1021</v>
       </c>
       <c r="I8" t="n">
-        <v>1114</v>
+        <v>852</v>
       </c>
       <c r="J8" t="n">
-        <v>1116</v>
+        <v>838</v>
       </c>
       <c r="K8" t="n">
-        <v>980</v>
+        <v>735</v>
       </c>
       <c r="L8" t="n">
-        <v>1021.2</v>
+        <v>838.8</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>1131</v>
+        <v>859</v>
       </c>
       <c r="C9" t="n">
-        <v>970</v>
+        <v>987</v>
       </c>
       <c r="D9" t="n">
-        <v>1083</v>
+        <v>849</v>
       </c>
       <c r="E9" t="n">
-        <v>909</v>
+        <v>798</v>
       </c>
       <c r="F9" t="n">
-        <v>1092</v>
+        <v>866</v>
       </c>
       <c r="G9" t="n">
-        <v>959</v>
+        <v>919</v>
       </c>
       <c r="H9" t="n">
-        <v>1187</v>
+        <v>926</v>
       </c>
       <c r="I9" t="n">
-        <v>1085</v>
+        <v>915</v>
       </c>
       <c r="J9" t="n">
-        <v>1010</v>
+        <v>882</v>
       </c>
       <c r="K9" t="n">
-        <v>828</v>
+        <v>796</v>
       </c>
       <c r="L9" t="n">
-        <v>1025.4</v>
+        <v>879.7</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>958</v>
+        <v>738</v>
       </c>
       <c r="C10" t="n">
-        <v>1034</v>
+        <v>897</v>
       </c>
       <c r="D10" t="n">
-        <v>908</v>
+        <v>838</v>
       </c>
       <c r="E10" t="n">
-        <v>981</v>
+        <v>721</v>
       </c>
       <c r="F10" t="n">
-        <v>923</v>
+        <v>906</v>
       </c>
       <c r="G10" t="n">
-        <v>1040</v>
+        <v>757</v>
       </c>
       <c r="H10" t="n">
-        <v>1047</v>
+        <v>790</v>
       </c>
       <c r="I10" t="n">
-        <v>848</v>
+        <v>795</v>
       </c>
       <c r="J10" t="n">
-        <v>923</v>
+        <v>1126</v>
       </c>
       <c r="K10" t="n">
-        <v>1043</v>
+        <v>995</v>
       </c>
       <c r="L10" t="n">
-        <v>970.5</v>
+        <v>856.3</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1101</v>
+        <v>936</v>
       </c>
       <c r="C11" t="n">
-        <v>998</v>
+        <v>1019</v>
       </c>
       <c r="D11" t="n">
-        <v>1133</v>
+        <v>912</v>
       </c>
       <c r="E11" t="n">
-        <v>1155</v>
+        <v>1082</v>
       </c>
       <c r="F11" t="n">
-        <v>960</v>
+        <v>908</v>
       </c>
       <c r="G11" t="n">
-        <v>1173</v>
+        <v>906</v>
       </c>
       <c r="H11" t="n">
-        <v>1051</v>
+        <v>876</v>
       </c>
       <c r="I11" t="n">
-        <v>1070</v>
+        <v>899</v>
       </c>
       <c r="J11" t="n">
-        <v>999</v>
+        <v>933</v>
       </c>
       <c r="K11" t="n">
-        <v>977</v>
+        <v>913</v>
       </c>
       <c r="L11" t="n">
-        <v>1061.7</v>
+        <v>938.4</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1015</v>
+        <v>957</v>
       </c>
       <c r="C12" t="n">
-        <v>1066</v>
+        <v>898</v>
       </c>
       <c r="D12" t="n">
-        <v>938</v>
+        <v>871</v>
       </c>
       <c r="E12" t="n">
-        <v>1136</v>
+        <v>906</v>
       </c>
       <c r="F12" t="n">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="G12" t="n">
-        <v>955</v>
+        <v>882</v>
       </c>
       <c r="H12" t="n">
-        <v>1117</v>
+        <v>937</v>
       </c>
       <c r="I12" t="n">
-        <v>1170</v>
+        <v>1075</v>
       </c>
       <c r="J12" t="n">
-        <v>981</v>
+        <v>836</v>
       </c>
       <c r="K12" t="n">
-        <v>1273</v>
+        <v>837</v>
       </c>
       <c r="L12" t="n">
-        <v>1067.3</v>
+        <v>921.8</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>1112</v>
+        <v>724</v>
       </c>
       <c r="C13" t="n">
-        <v>796</v>
+        <v>762</v>
       </c>
       <c r="D13" t="n">
-        <v>948</v>
+        <v>785</v>
       </c>
       <c r="E13" t="n">
-        <v>1092</v>
+        <v>984</v>
       </c>
       <c r="F13" t="n">
-        <v>967</v>
+        <v>793</v>
       </c>
       <c r="G13" t="n">
-        <v>1038</v>
+        <v>768</v>
       </c>
       <c r="H13" t="n">
-        <v>860</v>
+        <v>741</v>
       </c>
       <c r="I13" t="n">
-        <v>992</v>
+        <v>786</v>
       </c>
       <c r="J13" t="n">
-        <v>925</v>
+        <v>798</v>
       </c>
       <c r="K13" t="n">
-        <v>1035</v>
+        <v>748</v>
       </c>
       <c r="L13" t="n">
-        <v>976.5</v>
+        <v>788.9</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>1058</v>
+        <v>939</v>
       </c>
       <c r="C14" t="n">
-        <v>977</v>
+        <v>883</v>
       </c>
       <c r="D14" t="n">
-        <v>1095</v>
+        <v>782</v>
       </c>
       <c r="E14" t="n">
-        <v>1034</v>
+        <v>829</v>
       </c>
       <c r="F14" t="n">
-        <v>947</v>
+        <v>826</v>
       </c>
       <c r="G14" t="n">
-        <v>945</v>
+        <v>846</v>
       </c>
       <c r="H14" t="n">
-        <v>1084</v>
+        <v>920</v>
       </c>
       <c r="I14" t="n">
-        <v>1181</v>
+        <v>848</v>
       </c>
       <c r="J14" t="n">
-        <v>1070</v>
+        <v>830</v>
       </c>
       <c r="K14" t="n">
-        <v>1070</v>
+        <v>779</v>
       </c>
       <c r="L14" t="n">
-        <v>1046.1</v>
+        <v>848.2</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>1220</v>
+        <v>842</v>
       </c>
       <c r="C15" t="n">
-        <v>992</v>
+        <v>907</v>
       </c>
       <c r="D15" t="n">
-        <v>922</v>
+        <v>868</v>
       </c>
       <c r="E15" t="n">
-        <v>1079</v>
+        <v>873</v>
       </c>
       <c r="F15" t="n">
-        <v>1061</v>
+        <v>812</v>
       </c>
       <c r="G15" t="n">
-        <v>935</v>
+        <v>1064</v>
       </c>
       <c r="H15" t="n">
-        <v>1045</v>
+        <v>874</v>
       </c>
       <c r="I15" t="n">
-        <v>1076</v>
+        <v>883</v>
       </c>
       <c r="J15" t="n">
-        <v>929</v>
+        <v>1006</v>
       </c>
       <c r="K15" t="n">
-        <v>984</v>
+        <v>910</v>
       </c>
       <c r="L15" t="n">
-        <v>1024.3</v>
+        <v>903.9</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>993</v>
+        <v>914</v>
       </c>
       <c r="C16" t="n">
-        <v>972</v>
+        <v>878</v>
       </c>
       <c r="D16" t="n">
-        <v>1053</v>
+        <v>887</v>
       </c>
       <c r="E16" t="n">
-        <v>1130</v>
+        <v>924</v>
       </c>
       <c r="F16" t="n">
-        <v>896</v>
+        <v>1027</v>
       </c>
       <c r="G16" t="n">
-        <v>979</v>
+        <v>938</v>
       </c>
       <c r="H16" t="n">
-        <v>1051</v>
+        <v>1000</v>
       </c>
       <c r="I16" t="n">
-        <v>916</v>
+        <v>875</v>
       </c>
       <c r="J16" t="n">
-        <v>1030</v>
+        <v>1110</v>
       </c>
       <c r="K16" t="n">
-        <v>951</v>
+        <v>926</v>
       </c>
       <c r="L16" t="n">
-        <v>997.1</v>
+        <v>947.9</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>1348</v>
+        <v>926</v>
       </c>
       <c r="C17" t="n">
-        <v>998</v>
+        <v>864</v>
       </c>
       <c r="D17" t="n">
-        <v>1038</v>
+        <v>911</v>
       </c>
       <c r="E17" t="n">
-        <v>1055</v>
+        <v>944</v>
       </c>
       <c r="F17" t="n">
-        <v>915</v>
+        <v>967</v>
       </c>
       <c r="G17" t="n">
-        <v>1237</v>
+        <v>1083</v>
       </c>
       <c r="H17" t="n">
-        <v>1090</v>
+        <v>929</v>
       </c>
       <c r="I17" t="n">
-        <v>959</v>
+        <v>935</v>
       </c>
       <c r="J17" t="n">
-        <v>1262</v>
+        <v>820</v>
       </c>
       <c r="K17" t="n">
-        <v>1026</v>
+        <v>826</v>
       </c>
       <c r="L17" t="n">
-        <v>1092.8</v>
+        <v>920.5</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>1024</v>
+        <v>907</v>
       </c>
       <c r="C18" t="n">
-        <v>1103</v>
+        <v>942</v>
       </c>
       <c r="D18" t="n">
-        <v>1136</v>
+        <v>928</v>
       </c>
       <c r="E18" t="n">
-        <v>1086</v>
+        <v>865</v>
       </c>
       <c r="F18" t="n">
-        <v>994</v>
+        <v>938</v>
       </c>
       <c r="G18" t="n">
-        <v>1072</v>
+        <v>931</v>
       </c>
       <c r="H18" t="n">
-        <v>1021</v>
+        <v>845</v>
       </c>
       <c r="I18" t="n">
-        <v>1257</v>
+        <v>1008</v>
       </c>
       <c r="J18" t="n">
-        <v>1126</v>
+        <v>885</v>
       </c>
       <c r="K18" t="n">
-        <v>1077</v>
+        <v>921</v>
       </c>
       <c r="L18" t="n">
-        <v>1089.6</v>
+        <v>917</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>997</v>
+        <v>865</v>
       </c>
       <c r="C19" t="n">
-        <v>948</v>
+        <v>900</v>
       </c>
       <c r="D19" t="n">
-        <v>991</v>
+        <v>863</v>
       </c>
       <c r="E19" t="n">
-        <v>1015</v>
+        <v>755</v>
       </c>
       <c r="F19" t="n">
-        <v>726</v>
+        <v>812</v>
       </c>
       <c r="G19" t="n">
-        <v>874</v>
+        <v>798</v>
       </c>
       <c r="H19" t="n">
-        <v>829</v>
+        <v>1003</v>
       </c>
       <c r="I19" t="n">
-        <v>989</v>
+        <v>844</v>
       </c>
       <c r="J19" t="n">
-        <v>887</v>
+        <v>798</v>
       </c>
       <c r="K19" t="n">
-        <v>886</v>
+        <v>975</v>
       </c>
       <c r="L19" t="n">
-        <v>914.2</v>
+        <v>861.3</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>1109</v>
+        <v>1020</v>
       </c>
       <c r="C20" t="n">
-        <v>1191</v>
+        <v>1003</v>
       </c>
       <c r="D20" t="n">
-        <v>1114</v>
+        <v>953</v>
       </c>
       <c r="E20" t="n">
-        <v>1039</v>
+        <v>1118</v>
       </c>
       <c r="F20" t="n">
-        <v>1146</v>
+        <v>883</v>
       </c>
       <c r="G20" t="n">
-        <v>1056</v>
+        <v>875</v>
       </c>
       <c r="H20" t="n">
-        <v>1196</v>
+        <v>1052</v>
       </c>
       <c r="I20" t="n">
-        <v>1279</v>
+        <v>957</v>
       </c>
       <c r="J20" t="n">
-        <v>1050</v>
+        <v>1104</v>
       </c>
       <c r="K20" t="n">
-        <v>1245</v>
+        <v>924</v>
       </c>
       <c r="L20" t="n">
-        <v>1142.5</v>
+        <v>988.9</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>923</v>
+        <v>965</v>
       </c>
       <c r="C21" t="n">
-        <v>931</v>
+        <v>823</v>
       </c>
       <c r="D21" t="n">
+        <v>900</v>
+      </c>
+      <c r="E21" t="n">
+        <v>844</v>
+      </c>
+      <c r="F21" t="n">
         <v>921</v>
       </c>
-      <c r="E21" t="n">
-        <v>1015</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1171</v>
-      </c>
       <c r="G21" t="n">
-        <v>1269</v>
+        <v>911</v>
       </c>
       <c r="H21" t="n">
-        <v>1026</v>
+        <v>855</v>
       </c>
       <c r="I21" t="n">
-        <v>983</v>
+        <v>827</v>
       </c>
       <c r="J21" t="n">
-        <v>1026</v>
+        <v>973</v>
       </c>
       <c r="K21" t="n">
-        <v>882</v>
+        <v>904</v>
       </c>
       <c r="L21" t="n">
-        <v>1014.7</v>
+        <v>892.3</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>1076</v>
+        <v>843</v>
       </c>
       <c r="C22" t="n">
-        <v>954</v>
+        <v>800</v>
       </c>
       <c r="D22" t="n">
-        <v>1166</v>
+        <v>823</v>
       </c>
       <c r="E22" t="n">
-        <v>992</v>
+        <v>792</v>
       </c>
       <c r="F22" t="n">
-        <v>1009</v>
+        <v>864</v>
       </c>
       <c r="G22" t="n">
-        <v>1085</v>
+        <v>818</v>
       </c>
       <c r="H22" t="n">
-        <v>836</v>
+        <v>813</v>
       </c>
       <c r="I22" t="n">
-        <v>966</v>
+        <v>812</v>
       </c>
       <c r="J22" t="n">
-        <v>966</v>
+        <v>1065</v>
       </c>
       <c r="K22" t="n">
-        <v>1070</v>
+        <v>794</v>
       </c>
       <c r="L22" t="n">
-        <v>1012</v>
+        <v>842.4</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1155</v>
+        <v>921</v>
       </c>
       <c r="C23" t="n">
-        <v>1193</v>
+        <v>1007</v>
       </c>
       <c r="D23" t="n">
-        <v>1242</v>
+        <v>1127</v>
       </c>
       <c r="E23" t="n">
-        <v>1119</v>
+        <v>1030</v>
       </c>
       <c r="F23" t="n">
-        <v>1240</v>
+        <v>943</v>
       </c>
       <c r="G23" t="n">
-        <v>1097</v>
+        <v>1187</v>
       </c>
       <c r="H23" t="n">
-        <v>952</v>
+        <v>1003</v>
       </c>
       <c r="I23" t="n">
-        <v>1083</v>
+        <v>870</v>
       </c>
       <c r="J23" t="n">
-        <v>1180</v>
+        <v>1146</v>
       </c>
       <c r="K23" t="n">
-        <v>1203</v>
+        <v>1091</v>
       </c>
       <c r="L23" t="n">
-        <v>1146.4</v>
+        <v>1032.5</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>965</v>
+        <v>921</v>
       </c>
       <c r="C24" t="n">
-        <v>1188</v>
+        <v>987</v>
       </c>
       <c r="D24" t="n">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="E24" t="n">
+        <v>1028</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1016</v>
+      </c>
+      <c r="G24" t="n">
+        <v>950</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1164</v>
+      </c>
+      <c r="I24" t="n">
         <v>980</v>
       </c>
-      <c r="F24" t="n">
-        <v>1298</v>
-      </c>
-      <c r="G24" t="n">
-        <v>942</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1139</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1121</v>
-      </c>
       <c r="J24" t="n">
-        <v>1085</v>
+        <v>894</v>
       </c>
       <c r="K24" t="n">
-        <v>981</v>
+        <v>830</v>
       </c>
       <c r="L24" t="n">
-        <v>1077.6</v>
+        <v>984.8</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>1193</v>
+        <v>971</v>
       </c>
       <c r="C25" t="n">
-        <v>1068</v>
+        <v>930</v>
       </c>
       <c r="D25" t="n">
-        <v>963</v>
+        <v>818</v>
       </c>
       <c r="E25" t="n">
-        <v>1043</v>
+        <v>841</v>
       </c>
       <c r="F25" t="n">
-        <v>1053</v>
+        <v>904</v>
       </c>
       <c r="G25" t="n">
-        <v>960</v>
+        <v>846</v>
       </c>
       <c r="H25" t="n">
-        <v>1055</v>
+        <v>855</v>
       </c>
       <c r="I25" t="n">
-        <v>951</v>
+        <v>862</v>
       </c>
       <c r="J25" t="n">
-        <v>1174</v>
+        <v>1070</v>
       </c>
       <c r="K25" t="n">
-        <v>1125</v>
+        <v>780</v>
       </c>
       <c r="L25" t="n">
-        <v>1058.5</v>
+        <v>887.7</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>1087</v>
+        <v>842</v>
       </c>
       <c r="C26" t="n">
-        <v>1173</v>
+        <v>792</v>
       </c>
       <c r="D26" t="n">
-        <v>847</v>
+        <v>1027</v>
       </c>
       <c r="E26" t="n">
-        <v>975</v>
+        <v>799</v>
       </c>
       <c r="F26" t="n">
-        <v>1175</v>
+        <v>792</v>
       </c>
       <c r="G26" t="n">
-        <v>1109</v>
+        <v>723</v>
       </c>
       <c r="H26" t="n">
-        <v>1040</v>
+        <v>825</v>
       </c>
       <c r="I26" t="n">
-        <v>998</v>
+        <v>860</v>
       </c>
       <c r="J26" t="n">
-        <v>986</v>
+        <v>728</v>
       </c>
       <c r="K26" t="n">
-        <v>993</v>
+        <v>871</v>
       </c>
       <c r="L26" t="n">
-        <v>1038.3</v>
+        <v>825.9</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1242</v>
+        <v>939</v>
       </c>
       <c r="C27" t="n">
-        <v>1229</v>
+        <v>1041</v>
       </c>
       <c r="D27" t="n">
-        <v>1077</v>
+        <v>947</v>
       </c>
       <c r="E27" t="n">
-        <v>1081</v>
+        <v>789</v>
       </c>
       <c r="F27" t="n">
-        <v>1149</v>
+        <v>1096</v>
       </c>
       <c r="G27" t="n">
-        <v>1179</v>
+        <v>857</v>
       </c>
       <c r="H27" t="n">
-        <v>1114</v>
+        <v>908</v>
       </c>
       <c r="I27" t="n">
-        <v>1115</v>
+        <v>1009</v>
       </c>
       <c r="J27" t="n">
-        <v>1268</v>
+        <v>902</v>
       </c>
       <c r="K27" t="n">
-        <v>1042</v>
+        <v>900</v>
       </c>
       <c r="L27" t="n">
-        <v>1149.6</v>
+        <v>938.8</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>1261</v>
+        <v>1019</v>
       </c>
       <c r="C28" t="n">
-        <v>1058</v>
+        <v>899</v>
       </c>
       <c r="D28" t="n">
-        <v>1183</v>
+        <v>929</v>
       </c>
       <c r="E28" t="n">
-        <v>1149</v>
+        <v>975</v>
       </c>
       <c r="F28" t="n">
-        <v>1117</v>
+        <v>883</v>
       </c>
       <c r="G28" t="n">
-        <v>1079</v>
+        <v>879</v>
       </c>
       <c r="H28" t="n">
-        <v>1074</v>
+        <v>936</v>
       </c>
       <c r="I28" t="n">
-        <v>1163</v>
+        <v>937</v>
       </c>
       <c r="J28" t="n">
-        <v>1050</v>
+        <v>806</v>
       </c>
       <c r="K28" t="n">
-        <v>1162</v>
+        <v>984</v>
       </c>
       <c r="L28" t="n">
-        <v>1129.6</v>
+        <v>924.7</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>896</v>
+        <v>792</v>
       </c>
       <c r="C29" t="n">
-        <v>993</v>
+        <v>1079</v>
       </c>
       <c r="D29" t="n">
-        <v>1054</v>
+        <v>818</v>
       </c>
       <c r="E29" t="n">
-        <v>1007</v>
+        <v>814</v>
       </c>
       <c r="F29" t="n">
-        <v>1042</v>
+        <v>1013</v>
       </c>
       <c r="G29" t="n">
-        <v>1018</v>
+        <v>762</v>
       </c>
       <c r="H29" t="n">
-        <v>1040</v>
+        <v>751</v>
       </c>
       <c r="I29" t="n">
-        <v>1091</v>
+        <v>802</v>
       </c>
       <c r="J29" t="n">
-        <v>950</v>
+        <v>844</v>
       </c>
       <c r="K29" t="n">
-        <v>1146</v>
+        <v>947</v>
       </c>
       <c r="L29" t="n">
-        <v>1023.7</v>
+        <v>862.2</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>1169</v>
+        <v>889</v>
       </c>
       <c r="C30" t="n">
-        <v>1030</v>
+        <v>862</v>
       </c>
       <c r="D30" t="n">
-        <v>1122</v>
+        <v>932</v>
       </c>
       <c r="E30" t="n">
-        <v>916</v>
+        <v>815</v>
       </c>
       <c r="F30" t="n">
-        <v>1152</v>
+        <v>836</v>
       </c>
       <c r="G30" t="n">
-        <v>1213</v>
+        <v>909</v>
       </c>
       <c r="H30" t="n">
-        <v>1191</v>
+        <v>856</v>
       </c>
       <c r="I30" t="n">
-        <v>1153</v>
+        <v>866</v>
       </c>
       <c r="J30" t="n">
-        <v>997</v>
+        <v>779</v>
       </c>
       <c r="K30" t="n">
-        <v>979</v>
+        <v>823</v>
       </c>
       <c r="L30" t="n">
-        <v>1092.2</v>
+        <v>856.7</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>969</v>
+        <v>876</v>
       </c>
       <c r="C31" t="n">
-        <v>914</v>
+        <v>779</v>
       </c>
       <c r="D31" t="n">
-        <v>920</v>
+        <v>905</v>
       </c>
       <c r="E31" t="n">
-        <v>909</v>
+        <v>875</v>
       </c>
       <c r="F31" t="n">
-        <v>1086</v>
+        <v>783</v>
       </c>
       <c r="G31" t="n">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H31" t="n">
-        <v>934</v>
+        <v>856</v>
       </c>
       <c r="I31" t="n">
-        <v>922</v>
+        <v>943</v>
       </c>
       <c r="J31" t="n">
-        <v>997</v>
+        <v>870</v>
       </c>
       <c r="K31" t="n">
-        <v>1064</v>
+        <v>935</v>
       </c>
       <c r="L31" t="n">
-        <v>957.8</v>
+        <v>868.4</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>919</v>
+        <v>821</v>
       </c>
       <c r="C32" t="n">
-        <v>1118</v>
+        <v>1063</v>
       </c>
       <c r="D32" t="n">
-        <v>898</v>
+        <v>961</v>
       </c>
       <c r="E32" t="n">
-        <v>972</v>
+        <v>889</v>
       </c>
       <c r="F32" t="n">
-        <v>1117</v>
+        <v>861</v>
       </c>
       <c r="G32" t="n">
-        <v>969</v>
+        <v>854</v>
       </c>
       <c r="H32" t="n">
-        <v>1166</v>
+        <v>895</v>
       </c>
       <c r="I32" t="n">
-        <v>1096</v>
+        <v>848</v>
       </c>
       <c r="J32" t="n">
-        <v>933</v>
+        <v>863</v>
       </c>
       <c r="K32" t="n">
-        <v>896</v>
+        <v>810</v>
       </c>
       <c r="L32" t="n">
-        <v>1008.4</v>
+        <v>886.5</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>1097</v>
+        <v>825</v>
       </c>
       <c r="C33" t="n">
-        <v>1242</v>
+        <v>882</v>
       </c>
       <c r="D33" t="n">
-        <v>1023</v>
+        <v>960</v>
       </c>
       <c r="E33" t="n">
-        <v>1144</v>
+        <v>916</v>
       </c>
       <c r="F33" t="n">
-        <v>982</v>
+        <v>1126</v>
       </c>
       <c r="G33" t="n">
-        <v>1102</v>
+        <v>980</v>
       </c>
       <c r="H33" t="n">
-        <v>1250</v>
+        <v>1077</v>
       </c>
       <c r="I33" t="n">
-        <v>971</v>
+        <v>952</v>
       </c>
       <c r="J33" t="n">
-        <v>1091</v>
+        <v>895</v>
       </c>
       <c r="K33" t="n">
-        <v>1146</v>
+        <v>788</v>
       </c>
       <c r="L33" t="n">
-        <v>1104.8</v>
+        <v>940.1</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>762</v>
+        <v>840</v>
       </c>
       <c r="C34" t="n">
-        <v>893</v>
+        <v>815</v>
       </c>
       <c r="D34" t="n">
-        <v>1015</v>
+        <v>1049</v>
       </c>
       <c r="E34" t="n">
-        <v>850</v>
+        <v>911</v>
       </c>
       <c r="F34" t="n">
-        <v>989</v>
+        <v>935</v>
       </c>
       <c r="G34" t="n">
-        <v>931</v>
+        <v>817</v>
       </c>
       <c r="H34" t="n">
-        <v>1024</v>
+        <v>745</v>
       </c>
       <c r="I34" t="n">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="J34" t="n">
-        <v>1041</v>
+        <v>933</v>
       </c>
       <c r="K34" t="n">
-        <v>1113</v>
+        <v>813</v>
       </c>
       <c r="L34" t="n">
-        <v>959.4</v>
+        <v>884.3</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>897</v>
+        <v>910</v>
       </c>
       <c r="C35" t="n">
-        <v>980</v>
+        <v>833</v>
       </c>
       <c r="D35" t="n">
-        <v>1094</v>
+        <v>830</v>
       </c>
       <c r="E35" t="n">
-        <v>859</v>
+        <v>813</v>
       </c>
       <c r="F35" t="n">
-        <v>1053</v>
+        <v>946</v>
       </c>
       <c r="G35" t="n">
-        <v>1029</v>
+        <v>938</v>
       </c>
       <c r="H35" t="n">
-        <v>996</v>
+        <v>839</v>
       </c>
       <c r="I35" t="n">
-        <v>1041</v>
+        <v>1148</v>
       </c>
       <c r="J35" t="n">
-        <v>962</v>
+        <v>753</v>
       </c>
       <c r="K35" t="n">
-        <v>1057</v>
+        <v>752</v>
       </c>
       <c r="L35" t="n">
-        <v>996.8</v>
+        <v>876.2</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1149</v>
+        <v>880</v>
       </c>
       <c r="C36" t="n">
-        <v>1035</v>
+        <v>932</v>
       </c>
       <c r="D36" t="n">
-        <v>1258</v>
+        <v>1065</v>
       </c>
       <c r="E36" t="n">
-        <v>1248</v>
+        <v>975</v>
       </c>
       <c r="F36" t="n">
-        <v>1176</v>
+        <v>955</v>
       </c>
       <c r="G36" t="n">
-        <v>1085</v>
+        <v>1066</v>
       </c>
       <c r="H36" t="n">
-        <v>1265</v>
+        <v>954</v>
       </c>
       <c r="I36" t="n">
-        <v>1228</v>
+        <v>896</v>
       </c>
       <c r="J36" t="n">
-        <v>1059</v>
+        <v>1032</v>
       </c>
       <c r="K36" t="n">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="L36" t="n">
-        <v>1147.3</v>
+        <v>972.6</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C37" t="n">
+        <v>894</v>
+      </c>
+      <c r="D37" t="n">
+        <v>877</v>
+      </c>
+      <c r="E37" t="n">
+        <v>913</v>
+      </c>
+      <c r="F37" t="n">
+        <v>869</v>
+      </c>
+      <c r="G37" t="n">
+        <v>817</v>
+      </c>
+      <c r="H37" t="n">
         <v>896</v>
       </c>
-      <c r="D37" t="n">
-        <v>911</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1033</v>
-      </c>
-      <c r="F37" t="n">
-        <v>898</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1017</v>
-      </c>
-      <c r="H37" t="n">
-        <v>974</v>
-      </c>
       <c r="I37" t="n">
-        <v>931</v>
+        <v>816</v>
       </c>
       <c r="J37" t="n">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="K37" t="n">
-        <v>872</v>
+        <v>814</v>
       </c>
       <c r="L37" t="n">
-        <v>931.5</v>
+        <v>867.9</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>927</v>
+        <v>1069</v>
       </c>
       <c r="C38" t="n">
-        <v>1167</v>
+        <v>894</v>
       </c>
       <c r="D38" t="n">
-        <v>990</v>
+        <v>889</v>
       </c>
       <c r="E38" t="n">
-        <v>946</v>
+        <v>819</v>
       </c>
       <c r="F38" t="n">
-        <v>1085</v>
+        <v>824</v>
       </c>
       <c r="G38" t="n">
-        <v>1087</v>
+        <v>896</v>
       </c>
       <c r="H38" t="n">
-        <v>929</v>
+        <v>798</v>
       </c>
       <c r="I38" t="n">
-        <v>1199</v>
+        <v>903</v>
       </c>
       <c r="J38" t="n">
-        <v>1024</v>
+        <v>898</v>
       </c>
       <c r="K38" t="n">
-        <v>1076</v>
+        <v>870</v>
       </c>
       <c r="L38" t="n">
-        <v>1043</v>
+        <v>886</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>1247</v>
+        <v>872</v>
       </c>
       <c r="C39" t="n">
-        <v>992</v>
+        <v>847</v>
       </c>
       <c r="D39" t="n">
-        <v>799</v>
+        <v>888</v>
       </c>
       <c r="E39" t="n">
-        <v>843</v>
+        <v>810</v>
       </c>
       <c r="F39" t="n">
-        <v>1048</v>
+        <v>870</v>
       </c>
       <c r="G39" t="n">
-        <v>852</v>
+        <v>748</v>
       </c>
       <c r="H39" t="n">
-        <v>1041</v>
+        <v>840</v>
       </c>
       <c r="I39" t="n">
-        <v>1052</v>
+        <v>841</v>
       </c>
       <c r="J39" t="n">
-        <v>1087</v>
+        <v>830</v>
       </c>
       <c r="K39" t="n">
-        <v>1029</v>
+        <v>800</v>
       </c>
       <c r="L39" t="n">
-        <v>999</v>
+        <v>834.6</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>1074</v>
+        <v>896</v>
       </c>
       <c r="C40" t="n">
-        <v>1009</v>
+        <v>951</v>
       </c>
       <c r="D40" t="n">
-        <v>1173</v>
+        <v>885</v>
       </c>
       <c r="E40" t="n">
-        <v>1082</v>
+        <v>837</v>
       </c>
       <c r="F40" t="n">
-        <v>1358</v>
+        <v>798</v>
       </c>
       <c r="G40" t="n">
-        <v>1246</v>
+        <v>1000</v>
       </c>
       <c r="H40" t="n">
-        <v>960</v>
+        <v>850</v>
       </c>
       <c r="I40" t="n">
-        <v>1213</v>
+        <v>1038</v>
       </c>
       <c r="J40" t="n">
-        <v>960</v>
+        <v>823</v>
       </c>
       <c r="K40" t="n">
-        <v>1025</v>
+        <v>814</v>
       </c>
       <c r="L40" t="n">
-        <v>1110</v>
+        <v>889.2</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>1060</v>
+        <v>854</v>
       </c>
       <c r="C41" t="n">
-        <v>1006</v>
+        <v>910</v>
       </c>
       <c r="D41" t="n">
-        <v>997</v>
+        <v>934</v>
       </c>
       <c r="E41" t="n">
-        <v>995</v>
+        <v>870</v>
       </c>
       <c r="F41" t="n">
-        <v>959</v>
+        <v>944</v>
       </c>
       <c r="G41" t="n">
-        <v>1050</v>
+        <v>847</v>
       </c>
       <c r="H41" t="n">
-        <v>1316</v>
+        <v>909</v>
       </c>
       <c r="I41" t="n">
-        <v>934</v>
+        <v>974</v>
       </c>
       <c r="J41" t="n">
-        <v>1027</v>
+        <v>876</v>
       </c>
       <c r="K41" t="n">
-        <v>996</v>
+        <v>946</v>
       </c>
       <c r="L41" t="n">
-        <v>1034</v>
+        <v>906.4</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>951</v>
+        <v>898</v>
       </c>
       <c r="C42" t="n">
-        <v>978</v>
+        <v>903</v>
       </c>
       <c r="D42" t="n">
-        <v>1068</v>
+        <v>963</v>
       </c>
       <c r="E42" t="n">
-        <v>986</v>
+        <v>860</v>
       </c>
       <c r="F42" t="n">
-        <v>865</v>
+        <v>771</v>
       </c>
       <c r="G42" t="n">
-        <v>1107</v>
+        <v>962</v>
       </c>
       <c r="H42" t="n">
-        <v>1074</v>
+        <v>904</v>
       </c>
       <c r="I42" t="n">
-        <v>1005</v>
+        <v>834</v>
       </c>
       <c r="J42" t="n">
-        <v>974</v>
+        <v>768</v>
       </c>
       <c r="K42" t="n">
-        <v>1053</v>
+        <v>751</v>
       </c>
       <c r="L42" t="n">
-        <v>1006.1</v>
+        <v>861.4</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>971</v>
+        <v>738</v>
       </c>
       <c r="C43" t="n">
-        <v>1143</v>
+        <v>803</v>
       </c>
       <c r="D43" t="n">
-        <v>899</v>
+        <v>758</v>
       </c>
       <c r="E43" t="n">
-        <v>929</v>
+        <v>880</v>
       </c>
       <c r="F43" t="n">
-        <v>1143</v>
+        <v>839</v>
       </c>
       <c r="G43" t="n">
-        <v>1101</v>
+        <v>774</v>
       </c>
       <c r="H43" t="n">
-        <v>1000</v>
+        <v>792</v>
       </c>
       <c r="I43" t="n">
-        <v>1001</v>
+        <v>772</v>
       </c>
       <c r="J43" t="n">
-        <v>998</v>
+        <v>962</v>
       </c>
       <c r="K43" t="n">
-        <v>917</v>
+        <v>935</v>
       </c>
       <c r="L43" t="n">
-        <v>1010.2</v>
+        <v>825.3</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>1025</v>
+        <v>1010</v>
       </c>
       <c r="C44" t="n">
-        <v>1008</v>
+        <v>846</v>
       </c>
       <c r="D44" t="n">
-        <v>1045</v>
+        <v>985</v>
       </c>
       <c r="E44" t="n">
-        <v>1089</v>
+        <v>1056</v>
       </c>
       <c r="F44" t="n">
-        <v>891</v>
+        <v>999</v>
       </c>
       <c r="G44" t="n">
-        <v>877</v>
+        <v>1023</v>
       </c>
       <c r="H44" t="n">
-        <v>1138</v>
+        <v>1036</v>
       </c>
       <c r="I44" t="n">
-        <v>1188</v>
+        <v>885</v>
       </c>
       <c r="J44" t="n">
-        <v>928</v>
+        <v>817</v>
       </c>
       <c r="K44" t="n">
-        <v>856</v>
+        <v>910</v>
       </c>
       <c r="L44" t="n">
-        <v>1004.5</v>
+        <v>956.7</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1148</v>
+        <v>1096</v>
       </c>
       <c r="C45" t="n">
-        <v>1080</v>
+        <v>987</v>
       </c>
       <c r="D45" t="n">
-        <v>1177</v>
+        <v>1070</v>
       </c>
       <c r="E45" t="n">
-        <v>1024</v>
+        <v>871</v>
       </c>
       <c r="F45" t="n">
-        <v>1016</v>
+        <v>902</v>
       </c>
       <c r="G45" t="n">
-        <v>997</v>
+        <v>850</v>
       </c>
       <c r="H45" t="n">
-        <v>924</v>
+        <v>827</v>
       </c>
       <c r="I45" t="n">
-        <v>843</v>
+        <v>1044</v>
       </c>
       <c r="J45" t="n">
-        <v>1024</v>
+        <v>979</v>
       </c>
       <c r="K45" t="n">
-        <v>974</v>
+        <v>981</v>
       </c>
       <c r="L45" t="n">
-        <v>1020.7</v>
+        <v>960.7</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
+        <v>940</v>
+      </c>
+      <c r="C46" t="n">
+        <v>807</v>
+      </c>
+      <c r="D46" t="n">
+        <v>820</v>
+      </c>
+      <c r="E46" t="n">
+        <v>953</v>
+      </c>
+      <c r="F46" t="n">
+        <v>825</v>
+      </c>
+      <c r="G46" t="n">
+        <v>841</v>
+      </c>
+      <c r="H46" t="n">
+        <v>855</v>
+      </c>
+      <c r="I46" t="n">
         <v>952</v>
       </c>
-      <c r="C46" t="n">
-        <v>984</v>
-      </c>
-      <c r="D46" t="n">
-        <v>1036</v>
-      </c>
-      <c r="E46" t="n">
-        <v>964</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1058</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1120</v>
-      </c>
-      <c r="H46" t="n">
-        <v>981</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1150</v>
-      </c>
       <c r="J46" t="n">
-        <v>868</v>
+        <v>844</v>
       </c>
       <c r="K46" t="n">
-        <v>1109</v>
+        <v>850</v>
       </c>
       <c r="L46" t="n">
-        <v>1022.2</v>
+        <v>868.7</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>1119</v>
+        <v>975</v>
       </c>
       <c r="C47" t="n">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="D47" t="n">
-        <v>1145</v>
+        <v>1071</v>
       </c>
       <c r="E47" t="n">
-        <v>1051</v>
+        <v>953</v>
       </c>
       <c r="F47" t="n">
-        <v>1124</v>
+        <v>964</v>
       </c>
       <c r="G47" t="n">
-        <v>1067</v>
+        <v>944</v>
       </c>
       <c r="H47" t="n">
-        <v>980</v>
+        <v>963</v>
       </c>
       <c r="I47" t="n">
-        <v>1012</v>
+        <v>925</v>
       </c>
       <c r="J47" t="n">
-        <v>1151</v>
+        <v>972</v>
       </c>
       <c r="K47" t="n">
-        <v>1160</v>
+        <v>914</v>
       </c>
       <c r="L47" t="n">
-        <v>1085</v>
+        <v>973</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>1317</v>
+        <v>982</v>
       </c>
       <c r="C48" t="n">
-        <v>1187</v>
+        <v>825</v>
       </c>
       <c r="D48" t="n">
-        <v>1278</v>
+        <v>837</v>
       </c>
       <c r="E48" t="n">
-        <v>856</v>
+        <v>779</v>
       </c>
       <c r="F48" t="n">
-        <v>1232</v>
+        <v>834</v>
       </c>
       <c r="G48" t="n">
-        <v>862</v>
+        <v>818</v>
       </c>
       <c r="H48" t="n">
-        <v>877</v>
+        <v>780</v>
       </c>
       <c r="I48" t="n">
-        <v>927</v>
+        <v>763</v>
       </c>
       <c r="J48" t="n">
-        <v>1192</v>
+        <v>951</v>
       </c>
       <c r="K48" t="n">
-        <v>1011</v>
+        <v>900</v>
       </c>
       <c r="L48" t="n">
-        <v>1073.9</v>
+        <v>846.9</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>1026</v>
+        <v>917</v>
       </c>
       <c r="C49" t="n">
-        <v>1157</v>
+        <v>956</v>
       </c>
       <c r="D49" t="n">
-        <v>1076</v>
+        <v>849</v>
       </c>
       <c r="E49" t="n">
-        <v>1077</v>
+        <v>1083</v>
       </c>
       <c r="F49" t="n">
-        <v>1060</v>
+        <v>861</v>
       </c>
       <c r="G49" t="n">
-        <v>1010</v>
+        <v>909</v>
       </c>
       <c r="H49" t="n">
-        <v>1136</v>
+        <v>914</v>
       </c>
       <c r="I49" t="n">
-        <v>1011</v>
+        <v>938</v>
       </c>
       <c r="J49" t="n">
-        <v>1118</v>
+        <v>812</v>
       </c>
       <c r="K49" t="n">
-        <v>1118</v>
+        <v>985</v>
       </c>
       <c r="L49" t="n">
-        <v>1078.9</v>
+        <v>922.4</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>1120</v>
+        <v>1029</v>
       </c>
       <c r="C50" t="n">
-        <v>1045</v>
+        <v>950</v>
       </c>
       <c r="D50" t="n">
-        <v>1005</v>
+        <v>900</v>
       </c>
       <c r="E50" t="n">
-        <v>942</v>
+        <v>881</v>
       </c>
       <c r="F50" t="n">
-        <v>1146</v>
+        <v>951</v>
       </c>
       <c r="G50" t="n">
-        <v>1037</v>
+        <v>937</v>
       </c>
       <c r="H50" t="n">
-        <v>984</v>
+        <v>820</v>
       </c>
       <c r="I50" t="n">
-        <v>838</v>
+        <v>944</v>
       </c>
       <c r="J50" t="n">
-        <v>922</v>
+        <v>946</v>
       </c>
       <c r="K50" t="n">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="L50" t="n">
-        <v>992</v>
+        <v>924.6</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>969</v>
+        <v>895</v>
       </c>
       <c r="C51" t="n">
-        <v>1086</v>
+        <v>877</v>
       </c>
       <c r="D51" t="n">
-        <v>997</v>
+        <v>853</v>
       </c>
       <c r="E51" t="n">
-        <v>875</v>
+        <v>843</v>
       </c>
       <c r="F51" t="n">
-        <v>1015</v>
+        <v>1002</v>
       </c>
       <c r="G51" t="n">
-        <v>992</v>
+        <v>855</v>
       </c>
       <c r="H51" t="n">
-        <v>1087</v>
+        <v>917</v>
       </c>
       <c r="I51" t="n">
-        <v>1179</v>
+        <v>882</v>
       </c>
       <c r="J51" t="n">
-        <v>1087</v>
+        <v>1045</v>
       </c>
       <c r="K51" t="n">
-        <v>1040</v>
+        <v>760</v>
       </c>
       <c r="L51" t="n">
-        <v>1032.7</v>
+        <v>892.9</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1069.94</v>
+        <v>904.66</v>
       </c>
       <c r="C52" t="n">
-        <v>1033.56</v>
+        <v>901.46</v>
       </c>
       <c r="D52" t="n">
-        <v>1037.1</v>
+        <v>914.6799999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>1015.78</v>
+        <v>880.66</v>
       </c>
       <c r="F52" t="n">
-        <v>1052.44</v>
+        <v>888.16</v>
       </c>
       <c r="G52" t="n">
-        <v>1041.64</v>
+        <v>883.78</v>
       </c>
       <c r="H52" t="n">
-        <v>1037.94</v>
+        <v>899.6</v>
       </c>
       <c r="I52" t="n">
-        <v>1043.12</v>
+        <v>898.34</v>
       </c>
       <c r="J52" t="n">
-        <v>1033.66</v>
+        <v>903.6</v>
       </c>
       <c r="K52" t="n">
-        <v>1036.74</v>
+        <v>875.62</v>
       </c>
       <c r="L52" t="n">
-        <v>1040.192</v>
+        <v>895.056</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>7.606476545333862</v>
+        <v>8.129398345947266</v>
       </c>
       <c r="C2" t="n">
-        <v>7.14985728263855</v>
+        <v>8.386664390563965</v>
       </c>
       <c r="D2" t="n">
-        <v>7.166733503341675</v>
+        <v>8.388704776763916</v>
       </c>
       <c r="E2" t="n">
-        <v>6.09587550163269</v>
+        <v>7.132947206497192</v>
       </c>
       <c r="F2" t="n">
-        <v>6.386681079864502</v>
+        <v>6.598559617996216</v>
       </c>
       <c r="G2" t="n">
-        <v>7.233613967895508</v>
+        <v>6.273478031158447</v>
       </c>
       <c r="H2" t="n">
-        <v>6.722080945968628</v>
+        <v>9.389691352844238</v>
       </c>
       <c r="I2" t="n">
-        <v>6.849029541015625</v>
+        <v>6.558506488800049</v>
       </c>
       <c r="J2" t="n">
-        <v>8.361597537994385</v>
+        <v>6.277880668640137</v>
       </c>
       <c r="K2" t="n">
-        <v>9.818498373031616</v>
+        <v>6.58718729019165</v>
       </c>
       <c r="L2" t="n">
-        <v>7.339044427871704</v>
+        <v>7.372301816940308</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>9.028952836990356</v>
+        <v>6.789690732955933</v>
       </c>
       <c r="C3" t="n">
-        <v>6.981849431991577</v>
+        <v>6.369807720184326</v>
       </c>
       <c r="D3" t="n">
-        <v>7.026328325271606</v>
+        <v>7.858719110488892</v>
       </c>
       <c r="E3" t="n">
-        <v>10.63194918632507</v>
+        <v>8.414693117141724</v>
       </c>
       <c r="F3" t="n">
-        <v>8.731040239334106</v>
+        <v>6.705947160720825</v>
       </c>
       <c r="G3" t="n">
-        <v>9.117372512817383</v>
+        <v>6.814586400985718</v>
       </c>
       <c r="H3" t="n">
-        <v>7.032567024230957</v>
+        <v>6.736901760101318</v>
       </c>
       <c r="I3" t="n">
-        <v>8.283920764923096</v>
+        <v>6.802282810211182</v>
       </c>
       <c r="J3" t="n">
-        <v>9.711464881896973</v>
+        <v>6.588116407394409</v>
       </c>
       <c r="K3" t="n">
-        <v>9.621787548065186</v>
+        <v>8.10143780708313</v>
       </c>
       <c r="L3" t="n">
-        <v>8.616723275184631</v>
+        <v>7.118218302726746</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>7.800606489181519</v>
+        <v>8.267875671386719</v>
       </c>
       <c r="C4" t="n">
-        <v>7.9755699634552</v>
+        <v>6.481021404266357</v>
       </c>
       <c r="D4" t="n">
-        <v>7.710992097854614</v>
+        <v>6.381134271621704</v>
       </c>
       <c r="E4" t="n">
-        <v>8.580071210861206</v>
+        <v>6.650262355804443</v>
       </c>
       <c r="F4" t="n">
-        <v>6.198291063308716</v>
+        <v>6.646962404251099</v>
       </c>
       <c r="G4" t="n">
-        <v>6.628914594650269</v>
+        <v>6.881741523742676</v>
       </c>
       <c r="H4" t="n">
-        <v>7.363225221633911</v>
+        <v>9.482821941375732</v>
       </c>
       <c r="I4" t="n">
-        <v>8.71199107170105</v>
+        <v>6.265145063400269</v>
       </c>
       <c r="J4" t="n">
-        <v>6.265347242355347</v>
+        <v>7.621274471282959</v>
       </c>
       <c r="K4" t="n">
-        <v>6.660243988037109</v>
+        <v>8.19477391242981</v>
       </c>
       <c r="L4" t="n">
-        <v>7.389525294303894</v>
+        <v>7.287301301956177</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>9.2503662109375</v>
+        <v>6.138178825378418</v>
       </c>
       <c r="C5" t="n">
-        <v>6.372709035873413</v>
+        <v>5.712264776229858</v>
       </c>
       <c r="D5" t="n">
-        <v>7.492403268814087</v>
+        <v>5.891360759735107</v>
       </c>
       <c r="E5" t="n">
-        <v>9.123459577560425</v>
+        <v>6.11757755279541</v>
       </c>
       <c r="F5" t="n">
-        <v>8.298794746398926</v>
+        <v>6.155579090118408</v>
       </c>
       <c r="G5" t="n">
-        <v>8.997302293777466</v>
+        <v>6.169235467910767</v>
       </c>
       <c r="H5" t="n">
-        <v>6.052025318145752</v>
+        <v>6.299851655960083</v>
       </c>
       <c r="I5" t="n">
-        <v>5.637127161026001</v>
+        <v>6.04531192779541</v>
       </c>
       <c r="J5" t="n">
-        <v>6.381840944290161</v>
+        <v>6.387760162353516</v>
       </c>
       <c r="K5" t="n">
-        <v>8.534309864044189</v>
+        <v>7.451061487197876</v>
       </c>
       <c r="L5" t="n">
-        <v>7.614033842086792</v>
+        <v>6.236818170547485</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>8.867125034332275</v>
+        <v>5.515918016433716</v>
       </c>
       <c r="C6" t="n">
-        <v>5.768043279647827</v>
+        <v>5.830831527709961</v>
       </c>
       <c r="D6" t="n">
-        <v>6.028775691986084</v>
+        <v>5.511235475540161</v>
       </c>
       <c r="E6" t="n">
-        <v>8.713712930679321</v>
+        <v>5.896581172943115</v>
       </c>
       <c r="F6" t="n">
-        <v>8.361791610717773</v>
+        <v>5.839289426803589</v>
       </c>
       <c r="G6" t="n">
-        <v>6.210609436035156</v>
+        <v>5.893659591674805</v>
       </c>
       <c r="H6" t="n">
-        <v>5.699315309524536</v>
+        <v>7.084143161773682</v>
       </c>
       <c r="I6" t="n">
-        <v>6.53373384475708</v>
+        <v>5.478423833847046</v>
       </c>
       <c r="J6" t="n">
-        <v>6.000545740127563</v>
+        <v>5.767007350921631</v>
       </c>
       <c r="K6" t="n">
-        <v>8.56261134147644</v>
+        <v>5.346524000167847</v>
       </c>
       <c r="L6" t="n">
-        <v>7.074626421928405</v>
+        <v>5.816361355781555</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>8.991076707839966</v>
+        <v>7.206417083740234</v>
       </c>
       <c r="C7" t="n">
-        <v>6.852657318115234</v>
+        <v>10.05390405654907</v>
       </c>
       <c r="D7" t="n">
-        <v>7.194942474365234</v>
+        <v>9.520050048828125</v>
       </c>
       <c r="E7" t="n">
-        <v>8.514261484146118</v>
+        <v>7.356735706329346</v>
       </c>
       <c r="F7" t="n">
-        <v>9.820613622665405</v>
+        <v>6.730408191680908</v>
       </c>
       <c r="G7" t="n">
-        <v>9.651193618774414</v>
+        <v>7.57293701171875</v>
       </c>
       <c r="H7" t="n">
-        <v>7.580920934677124</v>
+        <v>7.406551837921143</v>
       </c>
       <c r="I7" t="n">
-        <v>7.048406600952148</v>
+        <v>7.207153558731079</v>
       </c>
       <c r="J7" t="n">
-        <v>9.372624397277832</v>
+        <v>7.343934059143066</v>
       </c>
       <c r="K7" t="n">
-        <v>9.683968305587769</v>
+        <v>7.374370574951172</v>
       </c>
       <c r="L7" t="n">
-        <v>8.471066546440124</v>
+        <v>7.777246212959289</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>9.524094104766846</v>
+        <v>6.576104879379272</v>
       </c>
       <c r="C8" t="n">
-        <v>8.91311240196228</v>
+        <v>8.143158197402954</v>
       </c>
       <c r="D8" t="n">
-        <v>9.388498783111572</v>
+        <v>9.609884977340698</v>
       </c>
       <c r="E8" t="n">
-        <v>6.56765604019165</v>
+        <v>6.910001993179321</v>
       </c>
       <c r="F8" t="n">
-        <v>6.82961106300354</v>
+        <v>6.744142055511475</v>
       </c>
       <c r="G8" t="n">
-        <v>7.253357172012329</v>
+        <v>7.614074945449829</v>
       </c>
       <c r="H8" t="n">
-        <v>10.31537747383118</v>
+        <v>8.317756175994873</v>
       </c>
       <c r="I8" t="n">
-        <v>7.839334964752197</v>
+        <v>7.351340770721436</v>
       </c>
       <c r="J8" t="n">
-        <v>9.979529619216919</v>
+        <v>6.32707953453064</v>
       </c>
       <c r="K8" t="n">
-        <v>6.722348928451538</v>
+        <v>6.469699382781982</v>
       </c>
       <c r="L8" t="n">
-        <v>8.333292055130006</v>
+        <v>7.406324291229248</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>9.272569894790649</v>
+        <v>6.631266117095947</v>
       </c>
       <c r="C9" t="n">
-        <v>8.123560667037964</v>
+        <v>8.840359449386597</v>
       </c>
       <c r="D9" t="n">
-        <v>8.136581897735596</v>
+        <v>7.623612403869629</v>
       </c>
       <c r="E9" t="n">
-        <v>7.554198980331421</v>
+        <v>7.612689018249512</v>
       </c>
       <c r="F9" t="n">
-        <v>7.602195739746094</v>
+        <v>6.575094938278198</v>
       </c>
       <c r="G9" t="n">
-        <v>6.856135845184326</v>
+        <v>6.939474821090698</v>
       </c>
       <c r="H9" t="n">
-        <v>7.901423931121826</v>
+        <v>7.47265362739563</v>
       </c>
       <c r="I9" t="n">
-        <v>8.489267110824585</v>
+        <v>7.804485559463501</v>
       </c>
       <c r="J9" t="n">
-        <v>7.238418579101562</v>
+        <v>7.211547613143921</v>
       </c>
       <c r="K9" t="n">
-        <v>7.081875085830688</v>
+        <v>7.013446807861328</v>
       </c>
       <c r="L9" t="n">
-        <v>7.825622773170471</v>
+        <v>7.372463035583496</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>6.462287425994873</v>
+        <v>6.788873195648193</v>
       </c>
       <c r="C10" t="n">
-        <v>7.363465547561646</v>
+        <v>7.653395652770996</v>
       </c>
       <c r="D10" t="n">
-        <v>6.856298685073853</v>
+        <v>7.501393795013428</v>
       </c>
       <c r="E10" t="n">
-        <v>6.925226449966431</v>
+        <v>6.353666067123413</v>
       </c>
       <c r="F10" t="n">
-        <v>5.978399038314819</v>
+        <v>5.970410346984863</v>
       </c>
       <c r="G10" t="n">
-        <v>7.299743413925171</v>
+        <v>6.633351802825928</v>
       </c>
       <c r="H10" t="n">
-        <v>6.728800296783447</v>
+        <v>6.765749931335449</v>
       </c>
       <c r="I10" t="n">
-        <v>6.686387062072754</v>
+        <v>6.064809799194336</v>
       </c>
       <c r="J10" t="n">
-        <v>7.782747268676758</v>
+        <v>8.8001868724823</v>
       </c>
       <c r="K10" t="n">
-        <v>8.635134696960449</v>
+        <v>8.336523532867432</v>
       </c>
       <c r="L10" t="n">
-        <v>7.07184898853302</v>
+        <v>7.086836099624634</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>8.888389587402344</v>
+        <v>6.403146266937256</v>
       </c>
       <c r="C11" t="n">
-        <v>6.338772296905518</v>
+        <v>9.798999547958374</v>
       </c>
       <c r="D11" t="n">
-        <v>8.750285387039185</v>
+        <v>7.743759393692017</v>
       </c>
       <c r="E11" t="n">
-        <v>10.2492995262146</v>
+        <v>9.893002033233643</v>
       </c>
       <c r="F11" t="n">
-        <v>7.039044857025146</v>
+        <v>6.537654876708984</v>
       </c>
       <c r="G11" t="n">
-        <v>8.181039571762085</v>
+        <v>7.225235462188721</v>
       </c>
       <c r="H11" t="n">
-        <v>6.943923234939575</v>
+        <v>7.48883318901062</v>
       </c>
       <c r="I11" t="n">
-        <v>6.646208047866821</v>
+        <v>6.430532455444336</v>
       </c>
       <c r="J11" t="n">
-        <v>6.680090427398682</v>
+        <v>6.289058208465576</v>
       </c>
       <c r="K11" t="n">
-        <v>6.581622838973999</v>
+        <v>6.708914756774902</v>
       </c>
       <c r="L11" t="n">
-        <v>7.629867577552796</v>
+        <v>7.451913619041443</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>8.395358085632324</v>
+        <v>8.861506223678589</v>
       </c>
       <c r="C12" t="n">
-        <v>8.151555776596069</v>
+        <v>7.640969276428223</v>
       </c>
       <c r="D12" t="n">
-        <v>6.905502319335938</v>
+        <v>7.196855306625366</v>
       </c>
       <c r="E12" t="n">
-        <v>8.400434255599976</v>
+        <v>7.182765245437622</v>
       </c>
       <c r="F12" t="n">
-        <v>8.70320463180542</v>
+        <v>8.836240530014038</v>
       </c>
       <c r="G12" t="n">
-        <v>8.992878675460815</v>
+        <v>6.819427251815796</v>
       </c>
       <c r="H12" t="n">
-        <v>8.293119668960571</v>
+        <v>7.335705757141113</v>
       </c>
       <c r="I12" t="n">
-        <v>9.890987157821655</v>
+        <v>9.918583631515503</v>
       </c>
       <c r="J12" t="n">
-        <v>7.418583869934082</v>
+        <v>6.705890655517578</v>
       </c>
       <c r="K12" t="n">
-        <v>9.849080324172974</v>
+        <v>6.611007213592529</v>
       </c>
       <c r="L12" t="n">
-        <v>8.500070476531983</v>
+        <v>7.710895109176636</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>8.427458524703979</v>
+        <v>6.128813028335571</v>
       </c>
       <c r="C13" t="n">
-        <v>6.97095251083374</v>
+        <v>6.624407291412354</v>
       </c>
       <c r="D13" t="n">
-        <v>6.742868185043335</v>
+        <v>6.784203290939331</v>
       </c>
       <c r="E13" t="n">
-        <v>8.350715398788452</v>
+        <v>7.890869379043579</v>
       </c>
       <c r="F13" t="n">
-        <v>6.836462497711182</v>
+        <v>6.514360189437866</v>
       </c>
       <c r="G13" t="n">
-        <v>7.710796117782593</v>
+        <v>6.562434911727905</v>
       </c>
       <c r="H13" t="n">
-        <v>6.656978845596313</v>
+        <v>5.846008062362671</v>
       </c>
       <c r="I13" t="n">
-        <v>7.800764322280884</v>
+        <v>5.902156114578247</v>
       </c>
       <c r="J13" t="n">
-        <v>6.076485395431519</v>
+        <v>7.349067211151123</v>
       </c>
       <c r="K13" t="n">
-        <v>7.552315235137939</v>
+        <v>5.843644618988037</v>
       </c>
       <c r="L13" t="n">
-        <v>7.312579703330994</v>
+        <v>6.544596409797668</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>7.573002099990845</v>
+        <v>8.343405723571777</v>
       </c>
       <c r="C14" t="n">
-        <v>7.079699039459229</v>
+        <v>7.166052579879761</v>
       </c>
       <c r="D14" t="n">
-        <v>9.109468221664429</v>
+        <v>7.583031177520752</v>
       </c>
       <c r="E14" t="n">
-        <v>6.408678770065308</v>
+        <v>7.201653480529785</v>
       </c>
       <c r="F14" t="n">
-        <v>7.734004974365234</v>
+        <v>7.035118579864502</v>
       </c>
       <c r="G14" t="n">
-        <v>6.952694177627563</v>
+        <v>7.327718019485474</v>
       </c>
       <c r="H14" t="n">
-        <v>7.307497024536133</v>
+        <v>7.585515022277832</v>
       </c>
       <c r="I14" t="n">
-        <v>8.402241706848145</v>
+        <v>7.223196268081665</v>
       </c>
       <c r="J14" t="n">
-        <v>7.034797668457031</v>
+        <v>7.257135629653931</v>
       </c>
       <c r="K14" t="n">
-        <v>8.155504941940308</v>
+        <v>6.964405536651611</v>
       </c>
       <c r="L14" t="n">
-        <v>7.575758862495422</v>
+        <v>7.368723201751709</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>8.600933074951172</v>
+        <v>7.559383869171143</v>
       </c>
       <c r="C15" t="n">
-        <v>8.125457763671875</v>
+        <v>6.658524751663208</v>
       </c>
       <c r="D15" t="n">
-        <v>7.052397012710571</v>
+        <v>6.320184946060181</v>
       </c>
       <c r="E15" t="n">
-        <v>8.694835662841797</v>
+        <v>7.617146015167236</v>
       </c>
       <c r="F15" t="n">
-        <v>7.633405685424805</v>
+        <v>6.448703527450562</v>
       </c>
       <c r="G15" t="n">
-        <v>7.658711194992065</v>
+        <v>9.309731006622314</v>
       </c>
       <c r="H15" t="n">
-        <v>7.942665576934814</v>
+        <v>6.622940540313721</v>
       </c>
       <c r="I15" t="n">
-        <v>6.296217679977417</v>
+        <v>7.335568189620972</v>
       </c>
       <c r="J15" t="n">
-        <v>6.400795459747314</v>
+        <v>8.313897609710693</v>
       </c>
       <c r="K15" t="n">
-        <v>6.30661940574646</v>
+        <v>6.344075918197632</v>
       </c>
       <c r="L15" t="n">
-        <v>7.471203851699829</v>
+        <v>7.253015637397766</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>7.430002927780151</v>
+        <v>6.770625829696655</v>
       </c>
       <c r="C16" t="n">
-        <v>7.071033954620361</v>
+        <v>6.705734491348267</v>
       </c>
       <c r="D16" t="n">
-        <v>7.722519636154175</v>
+        <v>7.011866569519043</v>
       </c>
       <c r="E16" t="n">
-        <v>6.862581253051758</v>
+        <v>7.824024200439453</v>
       </c>
       <c r="F16" t="n">
-        <v>6.543696165084839</v>
+        <v>7.718603134155273</v>
       </c>
       <c r="G16" t="n">
-        <v>6.782636404037476</v>
+        <v>7.567013502120972</v>
       </c>
       <c r="H16" t="n">
-        <v>6.83287239074707</v>
+        <v>7.026129484176636</v>
       </c>
       <c r="I16" t="n">
-        <v>6.716948747634888</v>
+        <v>7.152700424194336</v>
       </c>
       <c r="J16" t="n">
-        <v>6.407717943191528</v>
+        <v>8.024206638336182</v>
       </c>
       <c r="K16" t="n">
-        <v>6.945438623428345</v>
+        <v>6.765893697738647</v>
       </c>
       <c r="L16" t="n">
-        <v>6.931544804573059</v>
+        <v>7.256679797172547</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>11.31478309631348</v>
+        <v>7.905126094818115</v>
       </c>
       <c r="C17" t="n">
-        <v>7.498844861984253</v>
+        <v>7.287779331207275</v>
       </c>
       <c r="D17" t="n">
-        <v>9.923966884613037</v>
+        <v>7.068493366241455</v>
       </c>
       <c r="E17" t="n">
-        <v>8.495529174804688</v>
+        <v>7.037842035293579</v>
       </c>
       <c r="F17" t="n">
-        <v>7.321009397506714</v>
+        <v>7.062886476516724</v>
       </c>
       <c r="G17" t="n">
-        <v>9.770391225814819</v>
+        <v>9.297418355941772</v>
       </c>
       <c r="H17" t="n">
-        <v>9.041049003601074</v>
+        <v>7.730954647064209</v>
       </c>
       <c r="I17" t="n">
-        <v>7.277647018432617</v>
+        <v>8.28849983215332</v>
       </c>
       <c r="J17" t="n">
-        <v>10.59888434410095</v>
+        <v>6.88366436958313</v>
       </c>
       <c r="K17" t="n">
-        <v>8.589080810546875</v>
+        <v>6.961922645568848</v>
       </c>
       <c r="L17" t="n">
-        <v>8.983118581771851</v>
+        <v>7.552458715438843</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>7.619322776794434</v>
+        <v>7.077061176300049</v>
       </c>
       <c r="C18" t="n">
-        <v>10.27529788017273</v>
+        <v>6.294091939926147</v>
       </c>
       <c r="D18" t="n">
-        <v>7.519974708557129</v>
+        <v>7.482379913330078</v>
       </c>
       <c r="E18" t="n">
-        <v>8.740589618682861</v>
+        <v>7.236485958099365</v>
       </c>
       <c r="F18" t="n">
-        <v>7.200389862060547</v>
+        <v>7.254477739334106</v>
       </c>
       <c r="G18" t="n">
-        <v>8.018298625946045</v>
+        <v>6.352610349655151</v>
       </c>
       <c r="H18" t="n">
-        <v>7.301849603652954</v>
+        <v>6.795254230499268</v>
       </c>
       <c r="I18" t="n">
-        <v>9.120068550109863</v>
+        <v>8.33331823348999</v>
       </c>
       <c r="J18" t="n">
-        <v>8.055410623550415</v>
+        <v>6.494829177856445</v>
       </c>
       <c r="K18" t="n">
-        <v>7.356278657913208</v>
+        <v>6.596920967102051</v>
       </c>
       <c r="L18" t="n">
-        <v>8.120748090744019</v>
+        <v>6.991742968559265</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>7.257409811019897</v>
+        <v>6.419523239135742</v>
       </c>
       <c r="C19" t="n">
-        <v>6.88688850402832</v>
+        <v>7.223791360855103</v>
       </c>
       <c r="D19" t="n">
-        <v>8.14820671081543</v>
+        <v>6.5556800365448</v>
       </c>
       <c r="E19" t="n">
-        <v>6.113321542739868</v>
+        <v>6.383238077163696</v>
       </c>
       <c r="F19" t="n">
-        <v>6.489426612854004</v>
+        <v>6.199224710464478</v>
       </c>
       <c r="G19" t="n">
-        <v>6.657951354980469</v>
+        <v>6.290889978408813</v>
       </c>
       <c r="H19" t="n">
-        <v>5.93630313873291</v>
+        <v>8.345563411712646</v>
       </c>
       <c r="I19" t="n">
-        <v>7.123535633087158</v>
+        <v>6.285098075866699</v>
       </c>
       <c r="J19" t="n">
-        <v>6.035266876220703</v>
+        <v>6.594042301177979</v>
       </c>
       <c r="K19" t="n">
-        <v>6.660666227340698</v>
+        <v>7.182420969009399</v>
       </c>
       <c r="L19" t="n">
-        <v>6.730897641181945</v>
+        <v>6.747947216033936</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>6.490560531616211</v>
+        <v>9.342390060424805</v>
       </c>
       <c r="C20" t="n">
-        <v>10.77307319641113</v>
+        <v>7.555410385131836</v>
       </c>
       <c r="D20" t="n">
-        <v>8.496625661849976</v>
+        <v>6.810415267944336</v>
       </c>
       <c r="E20" t="n">
-        <v>7.445020198822021</v>
+        <v>8.406957864761353</v>
       </c>
       <c r="F20" t="n">
-        <v>8.599689722061157</v>
+        <v>6.641545057296753</v>
       </c>
       <c r="G20" t="n">
-        <v>7.539983510971069</v>
+        <v>6.726737260818481</v>
       </c>
       <c r="H20" t="n">
-        <v>8.8515625</v>
+        <v>10.04574656486511</v>
       </c>
       <c r="I20" t="n">
-        <v>10.53547859191895</v>
+        <v>8.169341802597046</v>
       </c>
       <c r="J20" t="n">
-        <v>7.372435569763184</v>
+        <v>9.012691974639893</v>
       </c>
       <c r="K20" t="n">
-        <v>9.324398040771484</v>
+        <v>7.234189033508301</v>
       </c>
       <c r="L20" t="n">
-        <v>8.542882752418517</v>
+        <v>7.994542527198791</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>6.451110124588013</v>
+        <v>7.801551342010498</v>
       </c>
       <c r="C21" t="n">
-        <v>7.198007345199585</v>
+        <v>6.928606748580933</v>
       </c>
       <c r="D21" t="n">
-        <v>6.679821252822876</v>
+        <v>6.350763082504272</v>
       </c>
       <c r="E21" t="n">
-        <v>8.404226303100586</v>
+        <v>6.62952184677124</v>
       </c>
       <c r="F21" t="n">
-        <v>9.203863859176636</v>
+        <v>7.090013265609741</v>
       </c>
       <c r="G21" t="n">
-        <v>8.814051866531372</v>
+        <v>6.532514095306396</v>
       </c>
       <c r="H21" t="n">
-        <v>9.197843313217163</v>
+        <v>6.96634840965271</v>
       </c>
       <c r="I21" t="n">
-        <v>7.139558792114258</v>
+        <v>7.575183629989624</v>
       </c>
       <c r="J21" t="n">
-        <v>7.289589166641235</v>
+        <v>7.699861764907837</v>
       </c>
       <c r="K21" t="n">
-        <v>6.845475435256958</v>
+        <v>7.112340450286865</v>
       </c>
       <c r="L21" t="n">
-        <v>7.722354745864868</v>
+        <v>7.068670463562012</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>6.437511444091797</v>
+        <v>6.227114200592041</v>
       </c>
       <c r="C22" t="n">
-        <v>5.392882823944092</v>
+        <v>5.895252227783203</v>
       </c>
       <c r="D22" t="n">
-        <v>8.213713407516479</v>
+        <v>6.360733509063721</v>
       </c>
       <c r="E22" t="n">
-        <v>5.93402886390686</v>
+        <v>6.350711345672607</v>
       </c>
       <c r="F22" t="n">
-        <v>5.530327320098877</v>
+        <v>6.309607028961182</v>
       </c>
       <c r="G22" t="n">
-        <v>5.954498529434204</v>
+        <v>6.414467811584473</v>
       </c>
       <c r="H22" t="n">
-        <v>5.915647506713867</v>
+        <v>6.811784982681274</v>
       </c>
       <c r="I22" t="n">
-        <v>6.293670654296875</v>
+        <v>6.049918413162231</v>
       </c>
       <c r="J22" t="n">
-        <v>6.453428030014038</v>
+        <v>8.059445381164551</v>
       </c>
       <c r="K22" t="n">
-        <v>5.991049528121948</v>
+        <v>6.1181800365448</v>
       </c>
       <c r="L22" t="n">
-        <v>6.211675810813904</v>
+        <v>6.459721493721008</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>7.617566347122192</v>
+        <v>6.825845241546631</v>
       </c>
       <c r="C23" t="n">
-        <v>9.485684871673584</v>
+        <v>9.195093631744385</v>
       </c>
       <c r="D23" t="n">
-        <v>9.950323581695557</v>
+        <v>9.721097469329834</v>
       </c>
       <c r="E23" t="n">
-        <v>7.740917921066284</v>
+        <v>9.096261978149414</v>
       </c>
       <c r="F23" t="n">
-        <v>11.40634965896606</v>
+        <v>8.468879222869873</v>
       </c>
       <c r="G23" t="n">
-        <v>8.879851579666138</v>
+        <v>9.624853849411011</v>
       </c>
       <c r="H23" t="n">
-        <v>6.940564870834351</v>
+        <v>8.865662574768066</v>
       </c>
       <c r="I23" t="n">
-        <v>8.410446405410767</v>
+        <v>7.399542570114136</v>
       </c>
       <c r="J23" t="n">
-        <v>10.48440170288086</v>
+        <v>10.89303779602051</v>
       </c>
       <c r="K23" t="n">
-        <v>9.548468828201294</v>
+        <v>10.40285348892212</v>
       </c>
       <c r="L23" t="n">
-        <v>9.04645757675171</v>
+        <v>9.049312782287597</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>7.102073192596436</v>
+        <v>7.76376485824585</v>
       </c>
       <c r="C24" t="n">
-        <v>11.44936966896057</v>
+        <v>8.130142450332642</v>
       </c>
       <c r="D24" t="n">
-        <v>8.894008159637451</v>
+        <v>9.192582368850708</v>
       </c>
       <c r="E24" t="n">
-        <v>7.562146663665771</v>
+        <v>8.493731498718262</v>
       </c>
       <c r="F24" t="n">
-        <v>10.33953309059143</v>
+        <v>8.233399391174316</v>
       </c>
       <c r="G24" t="n">
-        <v>7.793383836746216</v>
+        <v>7.045367956161499</v>
       </c>
       <c r="H24" t="n">
-        <v>10.26939463615417</v>
+        <v>9.177853107452393</v>
       </c>
       <c r="I24" t="n">
-        <v>8.897506713867188</v>
+        <v>6.675865173339844</v>
       </c>
       <c r="J24" t="n">
-        <v>9.824476003646851</v>
+        <v>6.814886331558228</v>
       </c>
       <c r="K24" t="n">
-        <v>6.994847059249878</v>
+        <v>6.778522968292236</v>
       </c>
       <c r="L24" t="n">
-        <v>8.912673902511596</v>
+        <v>7.830611610412598</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>7.816132545471191</v>
+        <v>6.570313453674316</v>
       </c>
       <c r="C25" t="n">
-        <v>7.163259744644165</v>
+        <v>6.449367523193359</v>
       </c>
       <c r="D25" t="n">
-        <v>6.975338459014893</v>
+        <v>5.816333055496216</v>
       </c>
       <c r="E25" t="n">
-        <v>6.558575868606567</v>
+        <v>6.362274646759033</v>
       </c>
       <c r="F25" t="n">
-        <v>7.166971206665039</v>
+        <v>7.076331377029419</v>
       </c>
       <c r="G25" t="n">
-        <v>7.009504079818726</v>
+        <v>6.405646324157715</v>
       </c>
       <c r="H25" t="n">
-        <v>6.887121915817261</v>
+        <v>6.496114015579224</v>
       </c>
       <c r="I25" t="n">
-        <v>7.054214477539062</v>
+        <v>6.61841607093811</v>
       </c>
       <c r="J25" t="n">
-        <v>9.021122694015503</v>
+        <v>7.575727462768555</v>
       </c>
       <c r="K25" t="n">
-        <v>7.259166240692139</v>
+        <v>6.381685495376587</v>
       </c>
       <c r="L25" t="n">
-        <v>7.291140723228454</v>
+        <v>6.575220942497253</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>8.507832765579224</v>
+        <v>6.456185340881348</v>
       </c>
       <c r="C26" t="n">
-        <v>8.640651226043701</v>
+        <v>6.23004937171936</v>
       </c>
       <c r="D26" t="n">
-        <v>6.944473743438721</v>
+        <v>7.863979578018188</v>
       </c>
       <c r="E26" t="n">
-        <v>6.875887155532837</v>
+        <v>6.109839677810669</v>
       </c>
       <c r="F26" t="n">
-        <v>9.707466840744019</v>
+        <v>7.037615060806274</v>
       </c>
       <c r="G26" t="n">
-        <v>8.21937108039856</v>
+        <v>6.635686635971069</v>
       </c>
       <c r="H26" t="n">
-        <v>8.656370878219604</v>
+        <v>6.396339178085327</v>
       </c>
       <c r="I26" t="n">
-        <v>7.641018867492676</v>
+        <v>6.60595965385437</v>
       </c>
       <c r="J26" t="n">
-        <v>7.401200532913208</v>
+        <v>6.17112922668457</v>
       </c>
       <c r="K26" t="n">
-        <v>6.900172233581543</v>
+        <v>7.370882272720337</v>
       </c>
       <c r="L26" t="n">
-        <v>7.949444532394409</v>
+        <v>6.687766599655151</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>10.16414785385132</v>
+        <v>6.556976795196533</v>
       </c>
       <c r="C27" t="n">
-        <v>10.53760933876038</v>
+        <v>8.512710094451904</v>
       </c>
       <c r="D27" t="n">
-        <v>9.877462387084961</v>
+        <v>7.778646230697632</v>
       </c>
       <c r="E27" t="n">
-        <v>8.996742486953735</v>
+        <v>7.681570291519165</v>
       </c>
       <c r="F27" t="n">
-        <v>8.636268854141235</v>
+        <v>9.508788108825684</v>
       </c>
       <c r="G27" t="n">
-        <v>9.247488498687744</v>
+        <v>6.854705572128296</v>
       </c>
       <c r="H27" t="n">
-        <v>9.185458421707153</v>
+        <v>6.809184789657593</v>
       </c>
       <c r="I27" t="n">
-        <v>7.613970518112183</v>
+        <v>9.008288860321045</v>
       </c>
       <c r="J27" t="n">
-        <v>9.194670915603638</v>
+        <v>7.123690843582153</v>
       </c>
       <c r="K27" t="n">
-        <v>7.16290807723999</v>
+        <v>8.856284618377686</v>
       </c>
       <c r="L27" t="n">
-        <v>9.061672735214234</v>
+        <v>7.869084620475769</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>11.20611619949341</v>
+        <v>8.834591388702393</v>
       </c>
       <c r="C28" t="n">
-        <v>7.984811067581177</v>
+        <v>7.680564641952515</v>
       </c>
       <c r="D28" t="n">
-        <v>10.87156558036804</v>
+        <v>7.01430606842041</v>
       </c>
       <c r="E28" t="n">
-        <v>9.441909313201904</v>
+        <v>7.890074014663696</v>
       </c>
       <c r="F28" t="n">
-        <v>8.427587032318115</v>
+        <v>7.503488779067993</v>
       </c>
       <c r="G28" t="n">
-        <v>7.407256841659546</v>
+        <v>6.91981840133667</v>
       </c>
       <c r="H28" t="n">
-        <v>9.282412052154541</v>
+        <v>7.080783367156982</v>
       </c>
       <c r="I28" t="n">
-        <v>9.19372034072876</v>
+        <v>7.990098237991333</v>
       </c>
       <c r="J28" t="n">
-        <v>7.840360164642334</v>
+        <v>7.426483392715454</v>
       </c>
       <c r="K28" t="n">
-        <v>7.391791105270386</v>
+        <v>7.388940811157227</v>
       </c>
       <c r="L28" t="n">
-        <v>8.904752969741821</v>
+        <v>7.572914910316467</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>7.705949068069458</v>
+        <v>6.866602897644043</v>
       </c>
       <c r="C29" t="n">
-        <v>7.319865703582764</v>
+        <v>8.919784784317017</v>
       </c>
       <c r="D29" t="n">
-        <v>9.749041080474854</v>
+        <v>6.954318284988403</v>
       </c>
       <c r="E29" t="n">
-        <v>8.405281782150269</v>
+        <v>6.850858926773071</v>
       </c>
       <c r="F29" t="n">
-        <v>7.515942335128784</v>
+        <v>8.048959255218506</v>
       </c>
       <c r="G29" t="n">
-        <v>8.341139554977417</v>
+        <v>6.858100175857544</v>
       </c>
       <c r="H29" t="n">
-        <v>9.882343530654907</v>
+        <v>6.940768241882324</v>
       </c>
       <c r="I29" t="n">
-        <v>13.42262244224548</v>
+        <v>7.972409725189209</v>
       </c>
       <c r="J29" t="n">
-        <v>7.121815204620361</v>
+        <v>7.49484395980835</v>
       </c>
       <c r="K29" t="n">
-        <v>7.169214248657227</v>
+        <v>9.232917785644531</v>
       </c>
       <c r="L29" t="n">
-        <v>8.663321495056152</v>
+        <v>7.6139564037323</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>10.03660583496094</v>
+        <v>6.861698150634766</v>
       </c>
       <c r="C30" t="n">
-        <v>8.817110538482666</v>
+        <v>6.93642783164978</v>
       </c>
       <c r="D30" t="n">
-        <v>7.681689977645874</v>
+        <v>7.328341245651245</v>
       </c>
       <c r="E30" t="n">
-        <v>7.224004745483398</v>
+        <v>7.268682718276978</v>
       </c>
       <c r="F30" t="n">
-        <v>9.839393854141235</v>
+        <v>7.168415546417236</v>
       </c>
       <c r="G30" t="n">
-        <v>9.116747856140137</v>
+        <v>6.997654676437378</v>
       </c>
       <c r="H30" t="n">
-        <v>8.956674098968506</v>
+        <v>7.083097457885742</v>
       </c>
       <c r="I30" t="n">
-        <v>8.286630392074585</v>
+        <v>7.225749969482422</v>
       </c>
       <c r="J30" t="n">
-        <v>7.187291860580444</v>
+        <v>6.502285957336426</v>
       </c>
       <c r="K30" t="n">
-        <v>6.887829780578613</v>
+        <v>6.978926658630371</v>
       </c>
       <c r="L30" t="n">
-        <v>8.403397893905639</v>
+        <v>7.035128021240235</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>6.815072536468506</v>
+        <v>6.81862735748291</v>
       </c>
       <c r="C31" t="n">
-        <v>6.143627405166626</v>
+        <v>6.848888397216797</v>
       </c>
       <c r="D31" t="n">
-        <v>7.796485900878906</v>
+        <v>6.613361835479736</v>
       </c>
       <c r="E31" t="n">
-        <v>8.153521537780762</v>
+        <v>7.1372971534729</v>
       </c>
       <c r="F31" t="n">
-        <v>9.548995018005371</v>
+        <v>6.650784015655518</v>
       </c>
       <c r="G31" t="n">
-        <v>6.039803981781006</v>
+        <v>7.403834104537964</v>
       </c>
       <c r="H31" t="n">
-        <v>8.052090644836426</v>
+        <v>6.992321968078613</v>
       </c>
       <c r="I31" t="n">
-        <v>6.765500783920288</v>
+        <v>6.78415060043335</v>
       </c>
       <c r="J31" t="n">
-        <v>6.701895236968994</v>
+        <v>7.396099328994751</v>
       </c>
       <c r="K31" t="n">
-        <v>8.068876981735229</v>
+        <v>7.024227857589722</v>
       </c>
       <c r="L31" t="n">
-        <v>7.408587002754212</v>
+        <v>6.966959261894226</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>6.588577508926392</v>
+        <v>6.501551866531372</v>
       </c>
       <c r="C32" t="n">
-        <v>8.619990825653076</v>
+        <v>11.67350745201111</v>
       </c>
       <c r="D32" t="n">
-        <v>6.38447380065918</v>
+        <v>8.791489362716675</v>
       </c>
       <c r="E32" t="n">
-        <v>6.933004140853882</v>
+        <v>6.755932807922363</v>
       </c>
       <c r="F32" t="n">
-        <v>9.482600212097168</v>
+        <v>6.646226406097412</v>
       </c>
       <c r="G32" t="n">
-        <v>7.221505403518677</v>
+        <v>7.588593006134033</v>
       </c>
       <c r="H32" t="n">
-        <v>9.101986885070801</v>
+        <v>6.754935503005981</v>
       </c>
       <c r="I32" t="n">
-        <v>8.313469171524048</v>
+        <v>7.671220541000366</v>
       </c>
       <c r="J32" t="n">
-        <v>6.249522924423218</v>
+        <v>6.189261913299561</v>
       </c>
       <c r="K32" t="n">
-        <v>6.58847975730896</v>
+        <v>6.368934869766235</v>
       </c>
       <c r="L32" t="n">
-        <v>7.54836106300354</v>
+        <v>7.494165372848511</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>9.445316076278687</v>
+        <v>6.600350141525269</v>
       </c>
       <c r="C33" t="n">
-        <v>9.472656726837158</v>
+        <v>7.326432704925537</v>
       </c>
       <c r="D33" t="n">
-        <v>6.8178391456604</v>
+        <v>8.997632741928101</v>
       </c>
       <c r="E33" t="n">
-        <v>9.502590179443359</v>
+        <v>7.200906991958618</v>
       </c>
       <c r="F33" t="n">
-        <v>6.938696146011353</v>
+        <v>8.898580551147461</v>
       </c>
       <c r="G33" t="n">
-        <v>7.416383266448975</v>
+        <v>8.795416116714478</v>
       </c>
       <c r="H33" t="n">
-        <v>10.07020902633667</v>
+        <v>9.811043739318848</v>
       </c>
       <c r="I33" t="n">
-        <v>7.25869083404541</v>
+        <v>6.950021266937256</v>
       </c>
       <c r="J33" t="n">
-        <v>9.298104286193848</v>
+        <v>6.714160442352295</v>
       </c>
       <c r="K33" t="n">
-        <v>9.08630633354187</v>
+        <v>7.155659914016724</v>
       </c>
       <c r="L33" t="n">
-        <v>8.530679202079773</v>
+        <v>7.845020461082458</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>6.152588367462158</v>
+        <v>5.994657516479492</v>
       </c>
       <c r="C34" t="n">
-        <v>7.42795205116272</v>
+        <v>6.185677051544189</v>
       </c>
       <c r="D34" t="n">
-        <v>8.908552885055542</v>
+        <v>7.345681667327881</v>
       </c>
       <c r="E34" t="n">
-        <v>5.83077335357666</v>
+        <v>6.790585517883301</v>
       </c>
       <c r="F34" t="n">
-        <v>6.611032485961914</v>
+        <v>7.445917367935181</v>
       </c>
       <c r="G34" t="n">
-        <v>6.493028402328491</v>
+        <v>7.155503034591675</v>
       </c>
       <c r="H34" t="n">
-        <v>8.204264640808105</v>
+        <v>7.362661361694336</v>
       </c>
       <c r="I34" t="n">
-        <v>5.933687925338745</v>
+        <v>8.294837951660156</v>
       </c>
       <c r="J34" t="n">
-        <v>7.755177974700928</v>
+        <v>6.872154951095581</v>
       </c>
       <c r="K34" t="n">
-        <v>8.582891464233398</v>
+        <v>5.892080307006836</v>
       </c>
       <c r="L34" t="n">
-        <v>7.189994955062867</v>
+        <v>6.933975672721862</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>7.329486131668091</v>
+        <v>8.284998893737793</v>
       </c>
       <c r="C35" t="n">
-        <v>7.421545267105103</v>
+        <v>7.065771818161011</v>
       </c>
       <c r="D35" t="n">
-        <v>10.51286268234253</v>
+        <v>7.278488159179688</v>
       </c>
       <c r="E35" t="n">
-        <v>7.271034479141235</v>
+        <v>7.508252859115601</v>
       </c>
       <c r="F35" t="n">
-        <v>9.206353664398193</v>
+        <v>7.92701268196106</v>
       </c>
       <c r="G35" t="n">
-        <v>7.75442910194397</v>
+        <v>8.017802000045776</v>
       </c>
       <c r="H35" t="n">
-        <v>8.484774112701416</v>
+        <v>7.014777421951294</v>
       </c>
       <c r="I35" t="n">
-        <v>7.27768611907959</v>
+        <v>9.061275243759155</v>
       </c>
       <c r="J35" t="n">
-        <v>7.392746686935425</v>
+        <v>7.065228223800659</v>
       </c>
       <c r="K35" t="n">
-        <v>9.707505702972412</v>
+        <v>7.107453584671021</v>
       </c>
       <c r="L35" t="n">
-        <v>8.235842394828797</v>
+        <v>7.633106088638305</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>10.04948902130127</v>
+        <v>7.924265623092651</v>
       </c>
       <c r="C36" t="n">
-        <v>8.963067293167114</v>
+        <v>9.453474044799805</v>
       </c>
       <c r="D36" t="n">
-        <v>10.31147885322571</v>
+        <v>10.30122423171997</v>
       </c>
       <c r="E36" t="n">
-        <v>7.598879098892212</v>
+        <v>8.057507514953613</v>
       </c>
       <c r="F36" t="n">
-        <v>10.14563012123108</v>
+        <v>8.029428720474243</v>
       </c>
       <c r="G36" t="n">
-        <v>9.250941753387451</v>
+        <v>9.619016885757446</v>
       </c>
       <c r="H36" t="n">
-        <v>9.525225639343262</v>
+        <v>9.260938405990601</v>
       </c>
       <c r="I36" t="n">
-        <v>9.347137928009033</v>
+        <v>7.451624631881714</v>
       </c>
       <c r="J36" t="n">
-        <v>8.876652956008911</v>
+        <v>9.765063762664795</v>
       </c>
       <c r="K36" t="n">
-        <v>8.809914588928223</v>
+        <v>9.22944450378418</v>
       </c>
       <c r="L36" t="n">
-        <v>9.287841725349427</v>
+        <v>8.909198832511901</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>6.83314061164856</v>
+        <v>6.995468854904175</v>
       </c>
       <c r="C37" t="n">
-        <v>7.078460454940796</v>
+        <v>6.180743455886841</v>
       </c>
       <c r="D37" t="n">
-        <v>6.697997808456421</v>
+        <v>6.450825452804565</v>
       </c>
       <c r="E37" t="n">
-        <v>8.294485092163086</v>
+        <v>6.550437688827515</v>
       </c>
       <c r="F37" t="n">
-        <v>7.644519090652466</v>
+        <v>6.369278192520142</v>
       </c>
       <c r="G37" t="n">
-        <v>6.602621555328369</v>
+        <v>6.661011934280396</v>
       </c>
       <c r="H37" t="n">
-        <v>6.567808628082275</v>
+        <v>7.082801818847656</v>
       </c>
       <c r="I37" t="n">
-        <v>5.854429006576538</v>
+        <v>6.449210643768311</v>
       </c>
       <c r="J37" t="n">
-        <v>5.897634267807007</v>
+        <v>6.48874306678772</v>
       </c>
       <c r="K37" t="n">
-        <v>6.134864330291748</v>
+        <v>6.351595878601074</v>
       </c>
       <c r="L37" t="n">
-        <v>6.760596084594726</v>
+        <v>6.558011698722839</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>7.076052188873291</v>
+        <v>7.666334629058838</v>
       </c>
       <c r="C38" t="n">
-        <v>6.879075765609741</v>
+        <v>6.820424795150757</v>
       </c>
       <c r="D38" t="n">
-        <v>7.181423664093018</v>
+        <v>6.837270975112915</v>
       </c>
       <c r="E38" t="n">
-        <v>7.128726243972778</v>
+        <v>6.552617311477661</v>
       </c>
       <c r="F38" t="n">
-        <v>9.197380065917969</v>
+        <v>6.813509702682495</v>
       </c>
       <c r="G38" t="n">
-        <v>7.22439169883728</v>
+        <v>7.193131685256958</v>
       </c>
       <c r="H38" t="n">
-        <v>6.699023962020874</v>
+        <v>6.748411655426025</v>
       </c>
       <c r="I38" t="n">
-        <v>9.304487943649292</v>
+        <v>6.324514389038086</v>
       </c>
       <c r="J38" t="n">
-        <v>8.820512533187866</v>
+        <v>6.705011606216431</v>
       </c>
       <c r="K38" t="n">
-        <v>9.891836404800415</v>
+        <v>7.196306467056274</v>
       </c>
       <c r="L38" t="n">
-        <v>7.940291047096252</v>
+        <v>6.885753321647644</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>10.39803338050842</v>
+        <v>6.402382612228394</v>
       </c>
       <c r="C39" t="n">
-        <v>8.802820682525635</v>
+        <v>6.362326145172119</v>
       </c>
       <c r="D39" t="n">
-        <v>6.259955644607544</v>
+        <v>6.580897092819214</v>
       </c>
       <c r="E39" t="n">
-        <v>6.965827703475952</v>
+        <v>6.39365029335022</v>
       </c>
       <c r="F39" t="n">
-        <v>6.936785697937012</v>
+        <v>7.187900543212891</v>
       </c>
       <c r="G39" t="n">
-        <v>6.784399271011353</v>
+        <v>6.076126337051392</v>
       </c>
       <c r="H39" t="n">
-        <v>9.213698625564575</v>
+        <v>6.855598449707031</v>
       </c>
       <c r="I39" t="n">
-        <v>6.353331089019775</v>
+        <v>7.542106151580811</v>
       </c>
       <c r="J39" t="n">
-        <v>8.712623119354248</v>
+        <v>7.325410604476929</v>
       </c>
       <c r="K39" t="n">
-        <v>6.513622522354126</v>
+        <v>6.211389541625977</v>
       </c>
       <c r="L39" t="n">
-        <v>7.694109773635864</v>
+        <v>6.693778777122498</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>8.708118200302124</v>
+        <v>7.501387119293213</v>
       </c>
       <c r="C40" t="n">
-        <v>6.559568166732788</v>
+        <v>9.054749250411987</v>
       </c>
       <c r="D40" t="n">
-        <v>7.856569051742554</v>
+        <v>7.338240146636963</v>
       </c>
       <c r="E40" t="n">
-        <v>7.902111530303955</v>
+        <v>7.488327264785767</v>
       </c>
       <c r="F40" t="n">
-        <v>10.57633304595947</v>
+        <v>7.023941993713379</v>
       </c>
       <c r="G40" t="n">
-        <v>8.309969425201416</v>
+        <v>8.957525253295898</v>
       </c>
       <c r="H40" t="n">
-        <v>7.221036911010742</v>
+        <v>7.20120644569397</v>
       </c>
       <c r="I40" t="n">
-        <v>9.750099420547485</v>
+        <v>8.096600770950317</v>
       </c>
       <c r="J40" t="n">
-        <v>6.408079862594604</v>
+        <v>8.036849737167358</v>
       </c>
       <c r="K40" t="n">
-        <v>8.731985092163086</v>
+        <v>7.065793514251709</v>
       </c>
       <c r="L40" t="n">
-        <v>8.202387070655822</v>
+        <v>7.776462149620056</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>7.822268009185791</v>
+        <v>7.486023187637329</v>
       </c>
       <c r="C41" t="n">
-        <v>8.704195261001587</v>
+        <v>8.04790997505188</v>
       </c>
       <c r="D41" t="n">
-        <v>8.720386981964111</v>
+        <v>8.726267337799072</v>
       </c>
       <c r="E41" t="n">
-        <v>7.447390556335449</v>
+        <v>7.267767667770386</v>
       </c>
       <c r="F41" t="n">
-        <v>8.511309146881104</v>
+        <v>8.154865264892578</v>
       </c>
       <c r="G41" t="n">
-        <v>7.873371124267578</v>
+        <v>7.864678859710693</v>
       </c>
       <c r="H41" t="n">
-        <v>10.24123597145081</v>
+        <v>7.414216995239258</v>
       </c>
       <c r="I41" t="n">
-        <v>7.381388425827026</v>
+        <v>8.572308540344238</v>
       </c>
       <c r="J41" t="n">
-        <v>8.333824157714844</v>
+        <v>7.676000118255615</v>
       </c>
       <c r="K41" t="n">
-        <v>7.534690618515015</v>
+        <v>7.435342311859131</v>
       </c>
       <c r="L41" t="n">
-        <v>8.257006025314331</v>
+        <v>7.864538025856018</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>5.923855781555176</v>
+        <v>5.654459714889526</v>
       </c>
       <c r="C42" t="n">
-        <v>5.932471990585327</v>
+        <v>6.450006008148193</v>
       </c>
       <c r="D42" t="n">
-        <v>8.916432619094849</v>
+        <v>8.52359938621521</v>
       </c>
       <c r="E42" t="n">
-        <v>7.067826747894287</v>
+        <v>5.925854444503784</v>
       </c>
       <c r="F42" t="n">
-        <v>5.494812965393066</v>
+        <v>5.238967180252075</v>
       </c>
       <c r="G42" t="n">
-        <v>8.847529888153076</v>
+        <v>8.490224599838257</v>
       </c>
       <c r="H42" t="n">
-        <v>6.234179735183716</v>
+        <v>6.663519620895386</v>
       </c>
       <c r="I42" t="n">
-        <v>7.737177133560181</v>
+        <v>5.67545485496521</v>
       </c>
       <c r="J42" t="n">
-        <v>5.770536184310913</v>
+        <v>5.431658983230591</v>
       </c>
       <c r="K42" t="n">
-        <v>7.182986974716187</v>
+        <v>6.074178218841553</v>
       </c>
       <c r="L42" t="n">
-        <v>6.910781002044677</v>
+        <v>6.412792301177978</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>7.042665719985962</v>
+        <v>6.234466552734375</v>
       </c>
       <c r="C43" t="n">
-        <v>7.956171751022339</v>
+        <v>6.887231588363647</v>
       </c>
       <c r="D43" t="n">
-        <v>6.251432180404663</v>
+        <v>6.245370626449585</v>
       </c>
       <c r="E43" t="n">
-        <v>6.469355344772339</v>
+        <v>6.771980285644531</v>
       </c>
       <c r="F43" t="n">
-        <v>8.449979782104492</v>
+        <v>7.381332635879517</v>
       </c>
       <c r="G43" t="n">
-        <v>6.48803973197937</v>
+        <v>6.267607688903809</v>
       </c>
       <c r="H43" t="n">
-        <v>8.273092985153198</v>
+        <v>6.373042345046997</v>
       </c>
       <c r="I43" t="n">
-        <v>7.972893476486206</v>
+        <v>6.547585248947144</v>
       </c>
       <c r="J43" t="n">
-        <v>6.837385177612305</v>
+        <v>7.397043466567993</v>
       </c>
       <c r="K43" t="n">
-        <v>6.52925968170166</v>
+        <v>7.536751985549927</v>
       </c>
       <c r="L43" t="n">
-        <v>7.227027583122253</v>
+        <v>6.764241242408753</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>8.175965070724487</v>
+        <v>8.808728218078613</v>
       </c>
       <c r="C44" t="n">
-        <v>9.029505252838135</v>
+        <v>7.249613285064697</v>
       </c>
       <c r="D44" t="n">
-        <v>8.347480058670044</v>
+        <v>8.284162521362305</v>
       </c>
       <c r="E44" t="n">
-        <v>8.663290739059448</v>
+        <v>8.017647981643677</v>
       </c>
       <c r="F44" t="n">
-        <v>7.451713562011719</v>
+        <v>9.295286417007446</v>
       </c>
       <c r="G44" t="n">
-        <v>6.586123704910278</v>
+        <v>8.806483507156372</v>
       </c>
       <c r="H44" t="n">
-        <v>8.163230895996094</v>
+        <v>8.275593280792236</v>
       </c>
       <c r="I44" t="n">
-        <v>9.070085763931274</v>
+        <v>7.338705539703369</v>
       </c>
       <c r="J44" t="n">
-        <v>7.975796461105347</v>
+        <v>6.491616487503052</v>
       </c>
       <c r="K44" t="n">
-        <v>6.433552742004395</v>
+        <v>6.352632761001587</v>
       </c>
       <c r="L44" t="n">
-        <v>7.989674425125122</v>
+        <v>7.892046999931336</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>8.951103687286377</v>
+        <v>10.01487469673157</v>
       </c>
       <c r="C45" t="n">
-        <v>7.48861837387085</v>
+        <v>9.423703670501709</v>
       </c>
       <c r="D45" t="n">
-        <v>10.82770299911499</v>
+        <v>11.13814401626587</v>
       </c>
       <c r="E45" t="n">
-        <v>7.303743839263916</v>
+        <v>7.184322357177734</v>
       </c>
       <c r="F45" t="n">
-        <v>7.076668977737427</v>
+        <v>7.77579927444458</v>
       </c>
       <c r="G45" t="n">
-        <v>6.644455194473267</v>
+        <v>6.458464622497559</v>
       </c>
       <c r="H45" t="n">
-        <v>6.973351001739502</v>
+        <v>6.950133800506592</v>
       </c>
       <c r="I45" t="n">
-        <v>6.894567966461182</v>
+        <v>8.689333438873291</v>
       </c>
       <c r="J45" t="n">
-        <v>8.571188449859619</v>
+        <v>7.665343046188354</v>
       </c>
       <c r="K45" t="n">
-        <v>8.33691668510437</v>
+        <v>8.627929449081421</v>
       </c>
       <c r="L45" t="n">
-        <v>7.90683171749115</v>
+        <v>8.392804837226867</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>7.4989013671875</v>
+        <v>9.115379810333252</v>
       </c>
       <c r="C46" t="n">
-        <v>8.037102937698364</v>
+        <v>6.840728282928467</v>
       </c>
       <c r="D46" t="n">
-        <v>6.875370502471924</v>
+        <v>7.097780227661133</v>
       </c>
       <c r="E46" t="n">
-        <v>6.90727972984314</v>
+        <v>6.553516387939453</v>
       </c>
       <c r="F46" t="n">
-        <v>8.71623682975769</v>
+        <v>7.094827651977539</v>
       </c>
       <c r="G46" t="n">
-        <v>9.117992162704468</v>
+        <v>7.595210552215576</v>
       </c>
       <c r="H46" t="n">
-        <v>6.985898494720459</v>
+        <v>7.362687349319458</v>
       </c>
       <c r="I46" t="n">
-        <v>9.358436346054077</v>
+        <v>8.472734451293945</v>
       </c>
       <c r="J46" t="n">
-        <v>7.351423740386963</v>
+        <v>7.109843969345093</v>
       </c>
       <c r="K46" t="n">
-        <v>8.775039672851562</v>
+        <v>7.083752393722534</v>
       </c>
       <c r="L46" t="n">
-        <v>7.962368178367615</v>
+        <v>7.432646107673645</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>8.50695013999939</v>
+        <v>7.87110710144043</v>
       </c>
       <c r="C47" t="n">
-        <v>7.426268815994263</v>
+        <v>9.411123752593994</v>
       </c>
       <c r="D47" t="n">
-        <v>9.244082689285278</v>
+        <v>7.977180242538452</v>
       </c>
       <c r="E47" t="n">
-        <v>8.690748453140259</v>
+        <v>7.589904308319092</v>
       </c>
       <c r="F47" t="n">
-        <v>9.396658658981323</v>
+        <v>8.482163429260254</v>
       </c>
       <c r="G47" t="n">
-        <v>8.705219984054565</v>
+        <v>7.844738006591797</v>
       </c>
       <c r="H47" t="n">
-        <v>6.968604803085327</v>
+        <v>8.304655075073242</v>
       </c>
       <c r="I47" t="n">
-        <v>8.928158760070801</v>
+        <v>7.01475715637207</v>
       </c>
       <c r="J47" t="n">
-        <v>8.458771705627441</v>
+        <v>7.417077302932739</v>
       </c>
       <c r="K47" t="n">
-        <v>9.228294849395752</v>
+        <v>7.397865533828735</v>
       </c>
       <c r="L47" t="n">
-        <v>8.555375885963439</v>
+        <v>7.93105719089508</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>8.320704698562622</v>
+        <v>7.220620393753052</v>
       </c>
       <c r="C48" t="n">
-        <v>9.604370355606079</v>
+        <v>6.357707738876343</v>
       </c>
       <c r="D48" t="n">
-        <v>11.33437609672546</v>
+        <v>6.772108554840088</v>
       </c>
       <c r="E48" t="n">
-        <v>6.257665872573853</v>
+        <v>6.382449865341187</v>
       </c>
       <c r="F48" t="n">
-        <v>9.106395721435547</v>
+        <v>6.423062801361084</v>
       </c>
       <c r="G48" t="n">
-        <v>6.720040082931519</v>
+        <v>6.156036615371704</v>
       </c>
       <c r="H48" t="n">
-        <v>6.582650184631348</v>
+        <v>6.555301666259766</v>
       </c>
       <c r="I48" t="n">
-        <v>6.541979551315308</v>
+        <v>6.13162636756897</v>
       </c>
       <c r="J48" t="n">
-        <v>9.22089672088623</v>
+        <v>7.283698081970215</v>
       </c>
       <c r="K48" t="n">
-        <v>6.644659519195557</v>
+        <v>6.627638578414917</v>
       </c>
       <c r="L48" t="n">
-        <v>8.033373880386353</v>
+        <v>6.591025066375733</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>8.137726783752441</v>
+        <v>6.993995666503906</v>
       </c>
       <c r="C49" t="n">
-        <v>7.866886138916016</v>
+        <v>7.282278776168823</v>
       </c>
       <c r="D49" t="n">
-        <v>8.880306959152222</v>
+        <v>6.79541015625</v>
       </c>
       <c r="E49" t="n">
-        <v>9.648157596588135</v>
+        <v>9.038012742996216</v>
       </c>
       <c r="F49" t="n">
-        <v>9.586219549179077</v>
+        <v>7.307627201080322</v>
       </c>
       <c r="G49" t="n">
-        <v>8.134398698806763</v>
+        <v>6.908583164215088</v>
       </c>
       <c r="H49" t="n">
-        <v>10.08005619049072</v>
+        <v>6.869147777557373</v>
       </c>
       <c r="I49" t="n">
-        <v>7.502808570861816</v>
+        <v>7.108232259750366</v>
       </c>
       <c r="J49" t="n">
-        <v>7.018957614898682</v>
+        <v>6.517309904098511</v>
       </c>
       <c r="K49" t="n">
-        <v>9.161073207855225</v>
+        <v>7.633848905563354</v>
       </c>
       <c r="L49" t="n">
-        <v>8.601659131050109</v>
+        <v>7.245444655418396</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>8.63785719871521</v>
+        <v>9.043330430984497</v>
       </c>
       <c r="C50" t="n">
-        <v>8.090081453323364</v>
+        <v>7.042087554931641</v>
       </c>
       <c r="D50" t="n">
-        <v>7.191773414611816</v>
+        <v>7.08759331703186</v>
       </c>
       <c r="E50" t="n">
-        <v>6.962496757507324</v>
+        <v>6.634202480316162</v>
       </c>
       <c r="F50" t="n">
-        <v>8.726087331771851</v>
+        <v>6.840925216674805</v>
       </c>
       <c r="G50" t="n">
-        <v>9.248480558395386</v>
+        <v>6.931846141815186</v>
       </c>
       <c r="H50" t="n">
-        <v>9.013543605804443</v>
+        <v>6.843731164932251</v>
       </c>
       <c r="I50" t="n">
-        <v>8.676573038101196</v>
+        <v>8.431347608566284</v>
       </c>
       <c r="J50" t="n">
-        <v>7.698071956634521</v>
+        <v>7.101080656051636</v>
       </c>
       <c r="K50" t="n">
-        <v>7.521854162216187</v>
+        <v>6.878044843673706</v>
       </c>
       <c r="L50" t="n">
-        <v>8.176681947708129</v>
+        <v>7.283418941497803</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>6.974630832672119</v>
+        <v>7.349201440811157</v>
       </c>
       <c r="C51" t="n">
-        <v>8.163069725036621</v>
+        <v>6.992108345031738</v>
       </c>
       <c r="D51" t="n">
-        <v>8.174026012420654</v>
+        <v>6.678879976272583</v>
       </c>
       <c r="E51" t="n">
-        <v>7.061420917510986</v>
+        <v>6.717908382415771</v>
       </c>
       <c r="F51" t="n">
-        <v>6.953924417495728</v>
+        <v>8.682059526443481</v>
       </c>
       <c r="G51" t="n">
-        <v>7.423226356506348</v>
+        <v>7.578030586242676</v>
       </c>
       <c r="H51" t="n">
-        <v>8.60383152961731</v>
+        <v>6.710947036743164</v>
       </c>
       <c r="I51" t="n">
-        <v>10.28075861930847</v>
+        <v>7.231273412704468</v>
       </c>
       <c r="J51" t="n">
-        <v>9.650096893310547</v>
+        <v>10.004075050354</v>
       </c>
       <c r="K51" t="n">
-        <v>8.356533288955688</v>
+        <v>6.785673856735229</v>
       </c>
       <c r="L51" t="n">
-        <v>8.164151859283447</v>
+        <v>7.473015761375427</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>8.144686489105224</v>
+        <v>7.282031197547912</v>
       </c>
       <c r="C52" t="n">
-        <v>7.886583194732666</v>
+        <v>7.48523323059082</v>
       </c>
       <c r="D52" t="n">
-        <v>8.1340363407135</v>
+        <v>7.50171347618103</v>
       </c>
       <c r="E52" t="n">
-        <v>7.753429355621338</v>
+        <v>7.20743495464325</v>
       </c>
       <c r="F52" t="n">
-        <v>8.116795783042908</v>
+        <v>7.206604037284851</v>
       </c>
       <c r="G52" t="n">
-        <v>7.743665375709534</v>
+        <v>7.258608717918396</v>
       </c>
       <c r="H52" t="n">
-        <v>7.938743662834168</v>
+        <v>7.396287627220154</v>
       </c>
       <c r="I52" t="n">
-        <v>7.92692006111145</v>
+        <v>7.271536164283752</v>
       </c>
       <c r="J52" t="n">
-        <v>7.759856791496277</v>
+        <v>7.273267874717712</v>
       </c>
       <c r="K52" t="n">
-        <v>7.852277007102966</v>
+        <v>7.134930000305176</v>
       </c>
       <c r="L52" t="n">
-        <v>7.925699406147003</v>
+        <v>7.301764728069307</v>
       </c>
     </row>
   </sheetData>
